--- a/data/trending_integrated_20261029_10.xlsx
+++ b/data/trending_integrated_20261029_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z17"/>
+  <dimension ref="A1:Z18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9560</v>
+        <v>9340</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+19.65%</t>
+          <t>'+16.90%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.67</v>
       </c>
       <c r="E2" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F2" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G2" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H2" t="n">
         <v>17.97</v>
@@ -610,7 +610,7 @@
         <v>18.64</v>
       </c>
       <c r="O2" t="n">
-        <v>95283407255</v>
+        <v>99211483755</v>
       </c>
       <c r="P2" t="n">
         <v>22450</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>광통신 섹터 강세 및 루멘텀 폭등에 따른 기대감. 서울반도체와의 비교 언급.</t>
+          <t>미국 광통신 기업 루멘텀의 급등에 따른 기대감 형성. LED 광원 및 희토류 관련 기술 경쟁 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['광통신', '루멘텀', '서울반도체']</t>
+          <t>['광통신', '루멘텀', 'LED']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38500</v>
+        <v>38400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+10.63%</t>
+          <t>'+10.34%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.74</v>
       </c>
       <c r="E3" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F3" t="n">
         <v>26</v>
       </c>
       <c r="G3" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H3" t="n">
         <v>5.8</v>
@@ -702,7 +702,7 @@
         <v>6.54</v>
       </c>
       <c r="O3" t="n">
-        <v>72858857600</v>
+        <v>77141673350</v>
       </c>
       <c r="P3" t="n">
         <v>126600</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>루멘텀 인수 관련 뉴스와 3분기 실적 개선에 따른 주가 상승 기대감.</t>
+          <t>루멘텀 폭등 및 마벨의 루멘텀 인수 관련 소식. RF머트리얼즈가 최대 수혜주로 언급되며 긍정적 전망 제시.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['루멘텀 인수', '실적 개선', '주가 상승']</t>
+          <t>['루멘텀', '인수', '수혜주']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8030</v>
+        <v>7750</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+7.79%</t>
+          <t>'+4.03%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-1.04</v>
       </c>
       <c r="E4" t="n">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="F4" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G4" t="n">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="H4" t="n">
         <v>0.42</v>
@@ -794,7 +794,7 @@
         <v>1.46</v>
       </c>
       <c r="O4" t="n">
-        <v>79097675470</v>
+        <v>83403335300</v>
       </c>
       <c r="P4" t="n">
         <v>10300</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>주가 급등락 및 적자 기업 관련 투자 논란. 대규모 매도세 및 투자 심리 악화.</t>
+          <t>하이닉스 물량 완판 및 광주반도체 속도전 돌입 관련 언급. 외인 매수세 유입에 대한 긍정적 반응과 일부 부정적 전망 혼재.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['적자 기업', '주가 변동성', '투자 논란']</t>
+          <t>['하이닉스', '광주반도체', '외인']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1534000</v>
+        <v>1524000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+3.16%</t>
+          <t>'+2.49%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -857,10 +857,10 @@
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="G5" t="n">
-        <v>1686</v>
+        <v>1606</v>
       </c>
       <c r="H5" t="n">
         <v>48.66</v>
@@ -886,7 +886,7 @@
         <v>48.61</v>
       </c>
       <c r="O5" t="n">
-        <v>2166465994500</v>
+        <v>2410914272500</v>
       </c>
       <c r="P5" t="n">
         <v>2987000</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>주가 상승 추세 지속 및 200만원 돌파 기대감. 자사주 매입 및 주주환원 정책 긍정적 영향.</t>
+          <t>고가 랠리에 대한 기대감 지속 및 200만원 목표 제시. 삼성전자 대비 우월한 흐름 및 주주환원 긍정 평가.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['반도체', '주주환원', '자사주 매입']</t>
+          <t>['반도체', '주주환원', '목표가']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14640</v>
+        <v>14620</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+1.74%</t>
+          <t>'+1.60%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.06</v>
       </c>
       <c r="E6" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F6" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G6" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H6" t="n">
         <v>8.050000000000001</v>
@@ -978,7 +978,7 @@
         <v>8.109999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>35313853275</v>
+        <v>38967456465</v>
       </c>
       <c r="P6" t="n">
         <v>49800</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>미국 시장 의료AI 급등 및 ESMO2026 스코프 관련 기대감을 바탕으로 한 긍정적 주가 전망.</t>
+          <t>의료 AI 분야의 템퍼스 AI 급등 및 나스닥 의료 AI 상승 언급. 3분기 실적 발표 기대감 존재.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['의료AI', 'ESMO2026', '주가 전망']</t>
+          <t>['의료 AI', '템퍼스 AI', '실적']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>530000</v>
+        <v>188900</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.75%</t>
+          <t>'-0.63%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.08</v>
+        <v>0.1</v>
       </c>
       <c r="E7" t="n">
-        <v>196</v>
+        <v>62</v>
       </c>
       <c r="F7" t="n">
-        <v>111</v>
+        <v>44</v>
       </c>
       <c r="G7" t="n">
-        <v>769</v>
+        <v>123</v>
       </c>
       <c r="H7" t="n">
-        <v>24.78</v>
+        <v>75</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>534000</v>
+        <v>190100</v>
       </c>
       <c r="K7" t="n">
-        <v>546000</v>
+        <v>189400</v>
       </c>
       <c r="L7" t="n">
-        <v>563000</v>
+        <v>197000</v>
       </c>
       <c r="M7" t="n">
-        <v>524000</v>
+        <v>186200</v>
       </c>
       <c r="N7" t="n">
-        <v>24.86</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>274477172500</v>
+        <v>620503414400</v>
       </c>
       <c r="P7" t="n">
-        <v>723000</v>
+        <v>243500</v>
       </c>
       <c r="Q7" t="n">
-        <v>259000</v>
+        <v>71000</v>
       </c>
       <c r="R7" t="n">
-        <v>6000</v>
+        <v>-484000</v>
       </c>
       <c r="S7" t="n">
-        <v>5000</v>
+        <v>-1000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>컨퍼런스콜 예상치 상회하는 3분기 실적 발표와 ESS, 전고체 관련 호재로 인한 긍정적 주가 전망.</t>
+          <t>우선주 소각 및 주주환원 정책에 대한 기대와 실망이 혼재. 기관 매도세 및 실적 발표 관련 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['컨퍼런스콜', '3분기 실적', 'ESS']</t>
+          <t>['우선주', '주주환원', '실적 발표']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>63400</v>
+        <v>63500</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-1.25%</t>
+          <t>'-1.09%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.54</v>
       </c>
       <c r="E8" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F8" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G8" t="n">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="H8" t="n">
         <v>41.55</v>
@@ -1162,7 +1162,7 @@
         <v>41.01</v>
       </c>
       <c r="O8" t="n">
-        <v>81419163950</v>
+        <v>87472791800</v>
       </c>
       <c r="P8" t="n">
         <v>67300</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>수주 공시 및 신고가 근접. 자사주 매입과 공매도 관련 이슈, 건설 섹터 내 강세 전망.</t>
+          <t>자사주 매입 및 소각 기대감에 따른 상승세. 수주 공시 및 신고가 경신 가능성 언급. 건설 섹터 내 강세.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['수주 공시', '자사주 매입', '신고가']</t>
+          <t>['자사주', '수주 공시', '신고가']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>187400</v>
+        <v>527000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.42%</t>
+          <t>'-1.31%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.1</v>
+        <v>-0.08</v>
       </c>
       <c r="E9" t="n">
-        <v>50</v>
+        <v>206</v>
       </c>
       <c r="F9" t="n">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="G9" t="n">
-        <v>107</v>
+        <v>840</v>
       </c>
       <c r="H9" t="n">
-        <v>75</v>
+        <v>24.78</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>190100</v>
+        <v>534000</v>
       </c>
       <c r="K9" t="n">
-        <v>189400</v>
+        <v>546000</v>
       </c>
       <c r="L9" t="n">
-        <v>197000</v>
+        <v>563000</v>
       </c>
       <c r="M9" t="n">
-        <v>186200</v>
+        <v>524000</v>
       </c>
       <c r="N9" t="n">
-        <v>74.90000000000001</v>
+        <v>24.86</v>
       </c>
       <c r="O9" t="n">
-        <v>502963043250</v>
+        <v>287565730000</v>
       </c>
       <c r="P9" t="n">
-        <v>243500</v>
+        <v>723000</v>
       </c>
       <c r="Q9" t="n">
-        <v>71000</v>
+        <v>259000</v>
       </c>
       <c r="R9" t="n">
-        <v>-484000</v>
+        <v>6000</v>
       </c>
       <c r="S9" t="n">
-        <v>-1000</v>
+        <v>5000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>삼성전자 주가 흐름에 따른 우선주 변동성. 주주환원 및 소각 기대감과 실적 관련 논의.</t>
+          <t>삼성SDI, 3분기 연결 영업이익 4,078억원으로 컨센서스 상회. ESS, 전고체 관련주 동반 급등 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['우선주', '주주환원', '실적']</t>
+          <t>['삼성SDI', '영업이익', '컨센서스']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,77 +1292,77 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>006400</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>238500</v>
+        <v>14780</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-1.45%</t>
+          <t>'-1.34%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.04</v>
+        <v>0.46</v>
       </c>
       <c r="E10" t="n">
-        <v>800</v>
+        <v>96</v>
       </c>
       <c r="F10" t="n">
-        <v>495</v>
+        <v>61</v>
       </c>
       <c r="G10" t="n">
-        <v>1614</v>
+        <v>540</v>
       </c>
       <c r="H10" t="n">
-        <v>46.19</v>
+        <v>3.33</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>242000</v>
+        <v>14980</v>
       </c>
       <c r="K10" t="n">
-        <v>241000</v>
+        <v>15120</v>
       </c>
       <c r="L10" t="n">
-        <v>249000</v>
+        <v>15950</v>
       </c>
       <c r="M10" t="n">
-        <v>237250</v>
+        <v>14650</v>
       </c>
       <c r="N10" t="n">
-        <v>46.15</v>
+        <v>2.87</v>
       </c>
       <c r="O10" t="n">
-        <v>1730861094000</v>
+        <v>110221406125</v>
       </c>
       <c r="P10" t="n">
-        <v>374500</v>
+        <v>31500</v>
       </c>
       <c r="Q10" t="n">
-        <v>94500</v>
+        <v>1819</v>
       </c>
       <c r="R10" t="n">
-        <v>166000</v>
+        <v>-213000</v>
       </c>
       <c r="S10" t="n">
-        <v>-505000</v>
+        <v>41000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>주주환원 정책 발표 기대감 속 실적 발표 후 주가 변동성. 하이닉스와의 비교 언급.</t>
+          <t>광통신 섹터의 강세와 루멘텀의 폭등에 따른 기대감. 삼성전자의 투자 및 연말 3만 돌파 전망.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,11 +1371,11 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['주주환원', '실적 발표', '배당']</t>
+          <t>['광통신', '루멘텀', '삼성전자']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14750</v>
+        <v>235500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-1.54%</t>
+          <t>'-2.69%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.46</v>
+        <v>0.04</v>
       </c>
       <c r="E11" t="n">
-        <v>94</v>
+        <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>60</v>
+        <v>548</v>
       </c>
       <c r="G11" t="n">
-        <v>521</v>
+        <v>1969</v>
       </c>
       <c r="H11" t="n">
-        <v>3.33</v>
+        <v>46.19</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>14980</v>
+        <v>242000</v>
       </c>
       <c r="K11" t="n">
-        <v>15120</v>
+        <v>241000</v>
       </c>
       <c r="L11" t="n">
-        <v>15950</v>
+        <v>249000</v>
       </c>
       <c r="M11" t="n">
-        <v>14650</v>
+        <v>235500</v>
       </c>
       <c r="N11" t="n">
-        <v>2.87</v>
+        <v>46.15</v>
       </c>
       <c r="O11" t="n">
-        <v>104397425150</v>
+        <v>2039007133250</v>
       </c>
       <c r="P11" t="n">
-        <v>31500</v>
+        <v>374500</v>
       </c>
       <c r="Q11" t="n">
-        <v>1819</v>
+        <v>94500</v>
       </c>
       <c r="R11" t="n">
-        <v>-213000</v>
+        <v>166000</v>
       </c>
       <c r="S11" t="n">
-        <v>41000</v>
+        <v>-505000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>광통신 섹터의 강세와 루멘텀의 폭등에 따른 기대감. 삼성전자의 투자 및 연말 3만 돌파 전망.</t>
+          <t>주주환원 정책 발표에 대한 실망감 증폭. 하이닉스와의 실적 비교 및 노조 관련 논란.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['광통신', '루멘텀', '삼성전자']</t>
+          <t>['주주환원', '실적 발표', '배당']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,90 +1476,90 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4040</v>
+        <v>25750</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.69%</t>
+          <t>'-3.56%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="F12" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="G12" t="n">
-        <v>159</v>
+        <v>132</v>
       </c>
       <c r="H12" t="n">
-        <v>2.2</v>
+        <v>12.23</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>4195</v>
+        <v>26700</v>
       </c>
       <c r="K12" t="n">
-        <v>4280</v>
+        <v>26350</v>
       </c>
       <c r="L12" t="n">
-        <v>4480</v>
+        <v>26350</v>
       </c>
       <c r="M12" t="n">
-        <v>4000</v>
+        <v>25450</v>
       </c>
       <c r="N12" t="n">
-        <v>1.2</v>
+        <v>12.3</v>
       </c>
       <c r="O12" t="n">
-        <v>133875080268</v>
+        <v>20924433400</v>
       </c>
       <c r="P12" t="n">
-        <v>8100</v>
+        <v>59300</v>
       </c>
       <c r="Q12" t="n">
-        <v>592</v>
+        <v>22000</v>
       </c>
       <c r="R12" t="n">
-        <v>-347000</v>
+        <v>-93000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-12000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>광통신 섹터 강세 및 루멘텀 폭등에 따른 수혜 기대. 5G 상용화 및 글로벌 공급 관련 뉴스.</t>
+          <t>3분기 실적 부진 및 화학 부문 적자 전환에 대한 우려. 기관/외인 매도세와 연관된 부정적 전망.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['광통신', '5G', '루멘텀']</t>
+          <t>['실적 발표', '태양광', '화학']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>009830</t>
         </is>
       </c>
     </row>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>15850</v>
+        <v>15860</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-4.00%</t>
+          <t>'-3.94%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.04</v>
       </c>
       <c r="E13" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F13" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G13" t="n">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="H13" t="n">
         <v>28.07</v>
@@ -1622,7 +1622,7 @@
         <v>28.03</v>
       </c>
       <c r="O13" t="n">
-        <v>20087458290</v>
+        <v>21726904060</v>
       </c>
       <c r="P13" t="n">
         <v>35350</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>연속적인 신저점 경신 및 주가 부진. 실적 및 향후 전망에 대한 부정적 의견.</t>
+          <t>매일 신저점 갱신에 대한 우려 및 상장 폐지 논란. 향후 전망에 대한 부정적 의견과 실적 발표 관련 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['조선주', '신저점', '실적 부진']</t>
+          <t>['조선주', '신저점', '실적 발표']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1667,31 +1667,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17630</v>
+        <v>3965</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-8.22%</t>
+          <t>'-5.48%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.46</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>96</v>
+        <v>66</v>
       </c>
       <c r="F14" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G14" t="n">
-        <v>77</v>
+        <v>170</v>
       </c>
       <c r="H14" t="n">
-        <v>0.65</v>
+        <v>2.2</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>19210</v>
+        <v>4195</v>
       </c>
       <c r="K14" t="n">
-        <v>19010</v>
+        <v>4280</v>
       </c>
       <c r="L14" t="n">
-        <v>19840</v>
+        <v>4480</v>
       </c>
       <c r="M14" t="n">
-        <v>17500</v>
+        <v>3960</v>
       </c>
       <c r="N14" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="O14" t="n">
-        <v>69869570030</v>
+        <v>139561596703</v>
       </c>
       <c r="P14" t="n">
-        <v>28800</v>
+        <v>8100</v>
       </c>
       <c r="Q14" t="n">
-        <v>11550</v>
+        <v>592</v>
       </c>
       <c r="R14" t="n">
-        <v>7000</v>
+        <v>-347000</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>보호 예수 물량 출회 및 반도체 시장 하락에 따른 주가 하락 전망.</t>
+          <t>광통신 섹터의 강세 및 루멘텀의 급등에 따른 기대감. 5G 상용화망 성공 및 글로벌 공급 시작 뉴스.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['보호 예수 물량', '반도체 하락', '주가 전망']</t>
+          <t>['광통신', '5G', '루멘텀']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>앤로보틱스</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1850</v>
+        <v>17320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-11.90%</t>
+          <t>'-9.84%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.28</v>
+        <v>-0.46</v>
       </c>
       <c r="E15" t="n">
+        <v>108</v>
+      </c>
+      <c r="F15" t="n">
         <v>43</v>
       </c>
-      <c r="F15" t="n">
-        <v>30</v>
-      </c>
       <c r="G15" t="n">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="H15" t="n">
-        <v>5.35</v>
+        <v>0.65</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,38 +1791,38 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>2100</v>
+        <v>19210</v>
       </c>
       <c r="K15" t="n">
-        <v>2120</v>
+        <v>19010</v>
       </c>
       <c r="L15" t="n">
-        <v>2130</v>
+        <v>19840</v>
       </c>
       <c r="M15" t="n">
-        <v>1846</v>
+        <v>17320</v>
       </c>
       <c r="N15" t="n">
-        <v>5.07</v>
+        <v>1.11</v>
       </c>
       <c r="O15" t="n">
-        <v>8551897770</v>
+        <v>72360716645</v>
       </c>
       <c r="P15" t="n">
-        <v>4980</v>
+        <v>28800</v>
       </c>
       <c r="Q15" t="n">
-        <v>810</v>
+        <v>11550</v>
       </c>
       <c r="R15" t="n">
-        <v>38000</v>
+        <v>7000</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>세계 최초 고방사 세라믹 코팅 로봇 개발 국책 프로젝트 선정 관련 정보와 부정적인 주가 전망 혼재.</t>
+          <t>반도체 시장 하락 및 개미 투자자 손절 언급. 하락 VI 발동 및 전량 매도 권유 등 부정적 심리 표출.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['로봇 개발', '국책 프로젝트', '주가 전망']</t>
+          <t>['반도체', '하락 VI', '개미']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,90 +1844,90 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>138360</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>앤로보틱스</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>53800</v>
+        <v>1877</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-12.38%</t>
+          <t>'-10.62%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.02</v>
+        <v>0.28</v>
       </c>
       <c r="E16" t="n">
-        <v>362</v>
+        <v>46</v>
       </c>
       <c r="F16" t="n">
-        <v>264</v>
+        <v>30</v>
       </c>
       <c r="G16" t="n">
-        <v>1007</v>
+        <v>106</v>
       </c>
       <c r="H16" t="n">
-        <v>22.34</v>
+        <v>5.35</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>61400</v>
+        <v>2100</v>
       </c>
       <c r="K16" t="n">
-        <v>60600</v>
+        <v>2120</v>
       </c>
       <c r="L16" t="n">
-        <v>60800</v>
+        <v>2130</v>
       </c>
       <c r="M16" t="n">
-        <v>53400</v>
+        <v>1846</v>
       </c>
       <c r="N16" t="n">
-        <v>22.32</v>
+        <v>5.07</v>
       </c>
       <c r="O16" t="n">
-        <v>136455716100</v>
+        <v>9022070103</v>
       </c>
       <c r="P16" t="n">
-        <v>139200</v>
+        <v>4980</v>
       </c>
       <c r="Q16" t="n">
-        <v>53400</v>
+        <v>810</v>
       </c>
       <c r="R16" t="n">
-        <v>-351000</v>
+        <v>38000</v>
       </c>
       <c r="S16" t="n">
-        <v>-92000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>체코 원전 시공 계약 파기 관련 논란 속 주가 하락. 정치적 이슈와 연관된 부정적 여론.</t>
+          <t>세계 최초 고방사 세라믹 코팅 로봇 개발 및 100억 국책 프로젝트 선정 관련 내용. 주가 하락 및 부정적 전망이 우세.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['체코 원전', '시공 계약', '정치 이슈']</t>
+          <t>['로봇', '국책 프로젝트', '세라믹 코팅']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>138360</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>11220</v>
+        <v>54100</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-21.37%</t>
+          <t>'-11.89%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.23</v>
+        <v>0.02</v>
       </c>
       <c r="E17" t="n">
-        <v>265</v>
+        <v>458</v>
       </c>
       <c r="F17" t="n">
-        <v>165</v>
+        <v>330</v>
       </c>
       <c r="G17" t="n">
-        <v>548</v>
+        <v>1266</v>
       </c>
       <c r="H17" t="n">
-        <v>9.6</v>
+        <v>22.34</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,38 +1975,38 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>14270</v>
+        <v>61400</v>
       </c>
       <c r="K17" t="n">
-        <v>14180</v>
+        <v>60600</v>
       </c>
       <c r="L17" t="n">
-        <v>14180</v>
+        <v>60800</v>
       </c>
       <c r="M17" t="n">
-        <v>11200</v>
+        <v>53400</v>
       </c>
       <c r="N17" t="n">
-        <v>9.83</v>
+        <v>22.32</v>
       </c>
       <c r="O17" t="n">
-        <v>139647049860</v>
+        <v>157302755100</v>
       </c>
       <c r="P17" t="n">
-        <v>40350</v>
+        <v>139200</v>
       </c>
       <c r="Q17" t="n">
-        <v>3320</v>
+        <v>53400</v>
       </c>
       <c r="R17" t="n">
-        <v>-653000</v>
+        <v>-351000</v>
       </c>
       <c r="S17" t="n">
-        <v>-79000</v>
+        <v>-92000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>체코 원전 시공 계약 파기 영향으로 인한 주가 하락 및 투자 심리 악화. 공매도 관련 논란.</t>
+          <t>체코 원전 시공 계약 불발 및 국내 건설사 관련 논란. 정치적 이슈와 연관된 부정적 전망.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,18 +2015,110 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['체코 원전', '시공 계약', '공매도']</t>
+          <t>['체코 원전', '시공 계약', '이재명']</t>
         </is>
       </c>
       <c r="X17" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>034020</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>10950</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>'-23.27%</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="E18" t="n">
+        <v>340</v>
+      </c>
+      <c r="F18" t="n">
+        <v>210</v>
+      </c>
+      <c r="G18" t="n">
+        <v>687</v>
+      </c>
+      <c r="H18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>14270</v>
+      </c>
+      <c r="K18" t="n">
+        <v>14180</v>
+      </c>
+      <c r="L18" t="n">
+        <v>14180</v>
+      </c>
+      <c r="M18" t="n">
+        <v>10940</v>
+      </c>
+      <c r="N18" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="O18" t="n">
+        <v>168056755355</v>
+      </c>
+      <c r="P18" t="n">
+        <v>40350</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3320</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-653000</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-79000</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>체코 원전 사업 관련 불확실성 증폭 및 목표가 하향 조정. 정부 정책 변화와 공매도 관련 논란.</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>['체코 원전', '목표가 하향', '공매도']</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
         <v>20</v>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>047040</t>
         </is>

--- a/data/trending_integrated_20261029_10.xlsx
+++ b/data/trending_integrated_20261029_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z18"/>
+  <dimension ref="A1:Z21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>씨티알모빌리티</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9340</v>
+        <v>4910</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+16.90%</t>
+          <t>'+24.78%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.67</v>
+        <v>-0.4</v>
       </c>
       <c r="E2" t="n">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="F2" t="n">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="G2" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="H2" t="n">
-        <v>17.97</v>
+        <v>0.62</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,47 +595,47 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>7990</v>
+        <v>3935</v>
       </c>
       <c r="K2" t="n">
-        <v>8270</v>
+        <v>4085</v>
       </c>
       <c r="L2" t="n">
-        <v>10380</v>
+        <v>5110</v>
       </c>
       <c r="M2" t="n">
-        <v>7990</v>
+        <v>4080</v>
       </c>
       <c r="N2" t="n">
-        <v>18.64</v>
+        <v>1.02</v>
       </c>
       <c r="O2" t="n">
-        <v>99211483755</v>
+        <v>5520129143</v>
       </c>
       <c r="P2" t="n">
-        <v>22450</v>
+        <v>10200</v>
       </c>
       <c r="Q2" t="n">
-        <v>1760</v>
+        <v>2900</v>
       </c>
       <c r="R2" t="n">
-        <v>135000</v>
+        <v>-1000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>미국 광통신 기업 루멘텀의 급등에 따른 기대감 형성. LED 광원 및 희토류 관련 기술 경쟁 언급.</t>
+          <t>부품 수주 및 PO 임박으로 인한 10배 상승 기대감. 실제 납품 사실 기반.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['광통신', '루멘텀', 'LED']</t>
+          <t>['부품 수주', 'PO', '10배 상승']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -648,90 +648,90 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>308170</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38400</v>
+        <v>9450</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+10.34%</t>
+          <t>'+18.27%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.74</v>
+        <v>-0.67</v>
       </c>
       <c r="E3" t="n">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="F3" t="n">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="G3" t="n">
-        <v>116</v>
+        <v>48</v>
       </c>
       <c r="H3" t="n">
-        <v>5.8</v>
+        <v>17.97</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>34800</v>
+        <v>7990</v>
       </c>
       <c r="K3" t="n">
-        <v>36600</v>
+        <v>8270</v>
       </c>
       <c r="L3" t="n">
-        <v>40200</v>
+        <v>10380</v>
       </c>
       <c r="M3" t="n">
-        <v>36200</v>
+        <v>7990</v>
       </c>
       <c r="N3" t="n">
-        <v>6.54</v>
+        <v>18.64</v>
       </c>
       <c r="O3" t="n">
-        <v>77141673350</v>
+        <v>103238896215</v>
       </c>
       <c r="P3" t="n">
-        <v>126600</v>
+        <v>22450</v>
       </c>
       <c r="Q3" t="n">
-        <v>15260</v>
+        <v>1760</v>
       </c>
       <c r="R3" t="n">
-        <v>52000</v>
+        <v>135000</v>
       </c>
       <c r="S3" t="n">
-        <v>41000</v>
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>루멘텀 폭등 및 마벨의 루멘텀 인수 관련 소식. RF머트리얼즈가 최대 수혜주로 언급되며 긍정적 전망 제시.</t>
+          <t>미국 광통신 업체 폭등에 따른 기대감. LED 광원 관련 경쟁사 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['루멘텀', '인수', '수혜주']</t>
+          <t>['LED 광원', '광통신', '호재']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>서산</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7750</v>
+        <v>37900</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+4.03%</t>
+          <t>'+8.91%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-1.04</v>
+        <v>-0.74</v>
       </c>
       <c r="E4" t="n">
-        <v>101</v>
+        <v>45</v>
       </c>
       <c r="F4" t="n">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="G4" t="n">
-        <v>152</v>
+        <v>123</v>
       </c>
       <c r="H4" t="n">
-        <v>0.42</v>
+        <v>5.8</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,51 +779,51 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>7450</v>
+        <v>34800</v>
       </c>
       <c r="K4" t="n">
-        <v>7470</v>
+        <v>36600</v>
       </c>
       <c r="L4" t="n">
-        <v>9680</v>
+        <v>40200</v>
       </c>
       <c r="M4" t="n">
-        <v>7360</v>
+        <v>36200</v>
       </c>
       <c r="N4" t="n">
-        <v>1.46</v>
+        <v>6.54</v>
       </c>
       <c r="O4" t="n">
-        <v>83403335300</v>
+        <v>82740659725</v>
       </c>
       <c r="P4" t="n">
-        <v>10300</v>
+        <v>126600</v>
       </c>
       <c r="Q4" t="n">
-        <v>952</v>
+        <v>15260</v>
       </c>
       <c r="R4" t="n">
-        <v>506000</v>
+        <v>52000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>41000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>하이닉스 물량 완판 및 광주반도체 속도전 돌입 관련 언급. 외인 매수세 유입에 대한 긍정적 반응과 일부 부정적 전망 혼재.</t>
+          <t>루멘텀 폭등에 따른 수혜주로 언급되며 20% 이상 상승 기대. 실적 오해도 해소되며 긍정적 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['하이닉스', '광주반도체', '외인']</t>
+          <t>['루멘텀', 'RF머트리얼즈', '실적']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,90 +832,90 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>079650</t>
+          <t>327260</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>서산</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1524000</v>
+        <v>8085</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+2.49%</t>
+          <t>'+8.52%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.05</v>
+        <v>-1.04</v>
       </c>
       <c r="E5" t="n">
-        <v>800</v>
+        <v>116</v>
       </c>
       <c r="F5" t="n">
-        <v>489</v>
+        <v>62</v>
       </c>
       <c r="G5" t="n">
-        <v>1606</v>
+        <v>173</v>
       </c>
       <c r="H5" t="n">
-        <v>48.66</v>
+        <v>0.42</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1487000</v>
+        <v>7450</v>
       </c>
       <c r="K5" t="n">
-        <v>1511000</v>
+        <v>7470</v>
       </c>
       <c r="L5" t="n">
-        <v>1587000</v>
+        <v>9680</v>
       </c>
       <c r="M5" t="n">
-        <v>1501000</v>
+        <v>7360</v>
       </c>
       <c r="N5" t="n">
-        <v>48.61</v>
+        <v>1.46</v>
       </c>
       <c r="O5" t="n">
-        <v>2410914272500</v>
+        <v>87371389800</v>
       </c>
       <c r="P5" t="n">
-        <v>2987000</v>
+        <v>10300</v>
       </c>
       <c r="Q5" t="n">
-        <v>501000</v>
+        <v>952</v>
       </c>
       <c r="R5" t="n">
-        <v>281000</v>
+        <v>506000</v>
       </c>
       <c r="S5" t="n">
-        <v>-134000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>고가 랠리에 대한 기대감 지속 및 200만원 목표 제시. 삼성전자 대비 우월한 흐름 및 주주환원 긍정 평가.</t>
+          <t>주가 상승과 하락에 대한 상반된 의견이 존재. 투자자들의 관망세 및 매도 의견이 혼재.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['반도체', '주주환원', '목표가']</t>
+          <t>['반도체', '대장주', '대량거래']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>079650</t>
         </is>
       </c>
     </row>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14620</v>
+        <v>14740</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+1.60%</t>
+          <t>'+2.43%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.06</v>
       </c>
       <c r="E6" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F6" t="n">
         <v>60</v>
       </c>
       <c r="G6" t="n">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="H6" t="n">
         <v>8.050000000000001</v>
@@ -978,7 +978,7 @@
         <v>8.109999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>38967456465</v>
+        <v>41278362625</v>
       </c>
       <c r="P6" t="n">
         <v>49800</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>의료 AI 분야의 템퍼스 AI 급등 및 나스닥 의료 AI 상승 언급. 3분기 실적 발표 기대감 존재.</t>
+          <t>의료 AI 섹터의 강세 및 긍정적인 차트 분석. 공매도 세력과의 경쟁 및 숏스퀴즈 기대감.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['의료 AI', '템퍼스 AI', '실적']</t>
+          <t>['의료 AI', '숏스퀴즈', '차트 분석']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>188900</v>
+        <v>1508000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.63%</t>
+          <t>'+1.41%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>62</v>
+        <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>44</v>
+        <v>490</v>
       </c>
       <c r="G7" t="n">
-        <v>123</v>
+        <v>1572</v>
       </c>
       <c r="H7" t="n">
-        <v>75</v>
+        <v>48.66</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>190100</v>
+        <v>1487000</v>
       </c>
       <c r="K7" t="n">
-        <v>189400</v>
+        <v>1511000</v>
       </c>
       <c r="L7" t="n">
-        <v>197000</v>
+        <v>1587000</v>
       </c>
       <c r="M7" t="n">
-        <v>186200</v>
+        <v>1501000</v>
       </c>
       <c r="N7" t="n">
-        <v>74.90000000000001</v>
+        <v>48.61</v>
       </c>
       <c r="O7" t="n">
-        <v>620503414400</v>
+        <v>2811864059500</v>
       </c>
       <c r="P7" t="n">
-        <v>243500</v>
+        <v>2987000</v>
       </c>
       <c r="Q7" t="n">
-        <v>71000</v>
+        <v>501000</v>
       </c>
       <c r="R7" t="n">
-        <v>-484000</v>
+        <v>281000</v>
       </c>
       <c r="S7" t="n">
-        <v>-1000</v>
+        <v>-134000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>우선주 소각 및 주주환원 정책에 대한 기대와 실망이 혼재. 기관 매도세 및 실적 발표 관련 언급.</t>
+          <t>주가 상승 추세 지속 및 200만원 돌파 기대감. 경쟁사 대비 우수한 주주환원 정책.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['우선주', '주주환원', '실적 발표']</t>
+          <t>['자사주 매입', '주주환원', '대장주']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>63500</v>
+        <v>64300</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-1.09%</t>
+          <t>'+0.16%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.54</v>
       </c>
       <c r="E8" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F8" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G8" t="n">
-        <v>339</v>
+        <v>354</v>
       </c>
       <c r="H8" t="n">
         <v>41.55</v>
@@ -1162,7 +1162,7 @@
         <v>41.01</v>
       </c>
       <c r="O8" t="n">
-        <v>87472791800</v>
+        <v>101098272300</v>
       </c>
       <c r="P8" t="n">
         <v>67300</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>자사주 매입 및 소각 기대감에 따른 상승세. 수주 공시 및 신고가 경신 가능성 언급. 건설 섹터 내 강세.</t>
+          <t>수주 공시 및 신고가 도전 기대감. 자사주 매입 지속 및 반도체 투자 확대 수혜.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['자사주', '수주 공시', '신고가']</t>
+          <t>['수주 공시', '신고가', '자사주 매입']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>527000</v>
+        <v>187000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.31%</t>
+          <t>'-1.63%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.08</v>
+        <v>0.1</v>
       </c>
       <c r="E9" t="n">
-        <v>206</v>
+        <v>68</v>
       </c>
       <c r="F9" t="n">
-        <v>116</v>
+        <v>47</v>
       </c>
       <c r="G9" t="n">
-        <v>840</v>
+        <v>154</v>
       </c>
       <c r="H9" t="n">
-        <v>24.78</v>
+        <v>75</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>534000</v>
+        <v>190100</v>
       </c>
       <c r="K9" t="n">
-        <v>546000</v>
+        <v>189400</v>
       </c>
       <c r="L9" t="n">
-        <v>563000</v>
+        <v>197000</v>
       </c>
       <c r="M9" t="n">
-        <v>524000</v>
+        <v>185900</v>
       </c>
       <c r="N9" t="n">
-        <v>24.86</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>287565730000</v>
+        <v>751467630900</v>
       </c>
       <c r="P9" t="n">
-        <v>723000</v>
+        <v>243500</v>
       </c>
       <c r="Q9" t="n">
-        <v>259000</v>
+        <v>71000</v>
       </c>
       <c r="R9" t="n">
-        <v>6000</v>
+        <v>-484000</v>
       </c>
       <c r="S9" t="n">
-        <v>5000</v>
+        <v>-1000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>삼성SDI, 3분기 연결 영업이익 4,078억원으로 컨센서스 상회. ESS, 전고체 관련주 동반 급등 언급.</t>
+          <t>우선주 소각 논의 및 주주환원 정책 지연에 대한 실망감.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['삼성SDI', '영업이익', '컨센서스']</t>
+          <t>['우선주 소각', '주주환원', '기관 매도']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14780</v>
+        <v>523000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-1.34%</t>
+          <t>'-2.06%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.46</v>
+        <v>-0.08</v>
       </c>
       <c r="E10" t="n">
-        <v>96</v>
+        <v>216</v>
       </c>
       <c r="F10" t="n">
-        <v>61</v>
+        <v>118</v>
       </c>
       <c r="G10" t="n">
-        <v>540</v>
+        <v>914</v>
       </c>
       <c r="H10" t="n">
-        <v>3.33</v>
+        <v>24.78</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>14980</v>
+        <v>534000</v>
       </c>
       <c r="K10" t="n">
-        <v>15120</v>
+        <v>546000</v>
       </c>
       <c r="L10" t="n">
-        <v>15950</v>
+        <v>563000</v>
       </c>
       <c r="M10" t="n">
-        <v>14650</v>
+        <v>520000</v>
       </c>
       <c r="N10" t="n">
-        <v>2.87</v>
+        <v>24.86</v>
       </c>
       <c r="O10" t="n">
-        <v>110221406125</v>
+        <v>305374487500</v>
       </c>
       <c r="P10" t="n">
-        <v>31500</v>
+        <v>723000</v>
       </c>
       <c r="Q10" t="n">
-        <v>1819</v>
+        <v>259000</v>
       </c>
       <c r="R10" t="n">
-        <v>-213000</v>
+        <v>6000</v>
       </c>
       <c r="S10" t="n">
-        <v>41000</v>
+        <v>5000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>광통신 섹터의 강세와 루멘텀의 폭등에 따른 기대감. 삼성전자의 투자 및 연말 3만 돌파 전망.</t>
+          <t>컨센서스를 상회하는 호실적 발표 및 흑자 전환. ESS, 전고체 관련주로서 긍정적인 전망 제시.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['광통신', '루멘텀', '삼성전자']</t>
+          <t>['실적', '컨퍼런스콜', 'ESS']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,77 +1384,77 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>006400</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>235500</v>
+        <v>14660</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-2.69%</t>
+          <t>'-2.14%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.04</v>
+        <v>0.46</v>
       </c>
       <c r="E11" t="n">
-        <v>800</v>
+        <v>105</v>
       </c>
       <c r="F11" t="n">
-        <v>548</v>
+        <v>67</v>
       </c>
       <c r="G11" t="n">
-        <v>1969</v>
+        <v>552</v>
       </c>
       <c r="H11" t="n">
-        <v>46.19</v>
+        <v>3.33</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>242000</v>
+        <v>14980</v>
       </c>
       <c r="K11" t="n">
-        <v>241000</v>
+        <v>15120</v>
       </c>
       <c r="L11" t="n">
-        <v>249000</v>
+        <v>15950</v>
       </c>
       <c r="M11" t="n">
-        <v>235500</v>
+        <v>14600</v>
       </c>
       <c r="N11" t="n">
-        <v>46.15</v>
+        <v>2.87</v>
       </c>
       <c r="O11" t="n">
-        <v>2039007133250</v>
+        <v>116668059850</v>
       </c>
       <c r="P11" t="n">
-        <v>374500</v>
+        <v>31500</v>
       </c>
       <c r="Q11" t="n">
-        <v>94500</v>
+        <v>1819</v>
       </c>
       <c r="R11" t="n">
-        <v>166000</v>
+        <v>-213000</v>
       </c>
       <c r="S11" t="n">
-        <v>-505000</v>
+        <v>41000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>주주환원 정책 발표에 대한 실망감 증폭. 하이닉스와의 실적 비교 및 노조 관련 논란.</t>
+          <t>메타버스 관련 뉴스 및 루멘텀 급등에 따른 기대감. 연말 목표가 3만 원 제시.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['주주환원', '실적 발표', '배당']</t>
+          <t>['광통신', '루멘텀', '메타버스']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25750</v>
+        <v>25850</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.56%</t>
+          <t>'-3.18%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G12" t="n">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="H12" t="n">
         <v>12.23</v>
@@ -1530,7 +1530,7 @@
         <v>12.3</v>
       </c>
       <c r="O12" t="n">
-        <v>20924433400</v>
+        <v>22138564600</v>
       </c>
       <c r="P12" t="n">
         <v>59300</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>3분기 실적 부진 및 화학 부문 적자 전환에 대한 우려. 기관/외인 매도세와 연관된 부정적 전망.</t>
+          <t>실적 발표 예정인 가운데, 시장의 기대와 우려가 혼재. 3분기 적자 예상 가능성 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['실적 발표', '태양광', '화학']</t>
+          <t>['실적 발표', '태양광', '적자 예상']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>15860</v>
+        <v>8860</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.94%</t>
+          <t>'-3.49%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.04</v>
+        <v>-0.37</v>
       </c>
       <c r="E13" t="n">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="F13" t="n">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="G13" t="n">
-        <v>216</v>
+        <v>114</v>
       </c>
       <c r="H13" t="n">
-        <v>28.07</v>
+        <v>0.37</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>16510</v>
+        <v>9180</v>
       </c>
       <c r="K13" t="n">
-        <v>16380</v>
+        <v>9200</v>
       </c>
       <c r="L13" t="n">
-        <v>16440</v>
+        <v>10900</v>
       </c>
       <c r="M13" t="n">
-        <v>15770</v>
+        <v>8730</v>
       </c>
       <c r="N13" t="n">
-        <v>28.03</v>
+        <v>0.74</v>
       </c>
       <c r="O13" t="n">
-        <v>21726904060</v>
+        <v>27612752875</v>
       </c>
       <c r="P13" t="n">
-        <v>35350</v>
+        <v>19380</v>
       </c>
       <c r="Q13" t="n">
-        <v>15770</v>
+        <v>3200</v>
       </c>
       <c r="R13" t="n">
-        <v>-348000</v>
+        <v>-32000</v>
       </c>
       <c r="S13" t="n">
-        <v>-70000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>매일 신저점 갱신에 대한 우려 및 상장 폐지 논란. 향후 전망에 대한 부정적 의견과 실적 발표 관련 언급.</t>
+          <t>주가 조작 의혹 및 외인 매도에 대한 불신. 정상적이지 않은 종목으로 인식.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['조선주', '신저점', '실적 발표']</t>
+          <t>['주가 조작', '외인 매도', '잡주']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,90 +1660,90 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3965</v>
+        <v>15930</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-5.48%</t>
+          <t>'-3.51%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0.04</v>
       </c>
       <c r="E14" t="n">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="F14" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="G14" t="n">
-        <v>170</v>
+        <v>229</v>
       </c>
       <c r="H14" t="n">
-        <v>2.2</v>
+        <v>28.07</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>4195</v>
+        <v>16510</v>
       </c>
       <c r="K14" t="n">
-        <v>4280</v>
+        <v>16380</v>
       </c>
       <c r="L14" t="n">
-        <v>4480</v>
+        <v>16440</v>
       </c>
       <c r="M14" t="n">
-        <v>3960</v>
+        <v>15770</v>
       </c>
       <c r="N14" t="n">
-        <v>1.2</v>
+        <v>28.03</v>
       </c>
       <c r="O14" t="n">
-        <v>139561596703</v>
+        <v>24196521085</v>
       </c>
       <c r="P14" t="n">
-        <v>8100</v>
+        <v>35350</v>
       </c>
       <c r="Q14" t="n">
-        <v>592</v>
+        <v>15770</v>
       </c>
       <c r="R14" t="n">
-        <v>-347000</v>
+        <v>-348000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-70000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>광통신 섹터의 강세 및 루멘텀의 급등에 따른 기대감. 5G 상용화망 성공 및 글로벌 공급 시작 뉴스.</t>
+          <t>신저점 갱신 및 실적 우려. 향후 전망에 대한 불확실성 증대.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['광통신', '5G', '루멘텀']</t>
+          <t>['신저점', '실적', '전망 불확실']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,90 +1752,90 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17320</v>
+        <v>232500</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-9.84%</t>
+          <t>'-3.93%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.46</v>
+        <v>0.04</v>
       </c>
       <c r="E15" t="n">
-        <v>108</v>
+        <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>43</v>
+        <v>587</v>
       </c>
       <c r="G15" t="n">
-        <v>77</v>
+        <v>2157</v>
       </c>
       <c r="H15" t="n">
-        <v>0.65</v>
+        <v>46.19</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>19210</v>
+        <v>242000</v>
       </c>
       <c r="K15" t="n">
-        <v>19010</v>
+        <v>241000</v>
       </c>
       <c r="L15" t="n">
-        <v>19840</v>
+        <v>249000</v>
       </c>
       <c r="M15" t="n">
-        <v>17320</v>
+        <v>232000</v>
       </c>
       <c r="N15" t="n">
-        <v>1.11</v>
+        <v>46.15</v>
       </c>
       <c r="O15" t="n">
-        <v>72360716645</v>
+        <v>2510060323000</v>
       </c>
       <c r="P15" t="n">
-        <v>28800</v>
+        <v>374500</v>
       </c>
       <c r="Q15" t="n">
-        <v>11550</v>
+        <v>94500</v>
       </c>
       <c r="R15" t="n">
-        <v>7000</v>
+        <v>166000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-505000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>반도체 시장 하락 및 개미 투자자 손절 언급. 하락 VI 발동 및 전량 매도 권유 등 부정적 심리 표출.</t>
+          <t>주주환원 정책 지연 및 미흡에 대한 강한 불만. 경쟁사 대비 저조한 성과.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['반도체', '하락 VI', '개미']</t>
+          <t>['주주환원', '성과급', '대국민 사기']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>앤로보틱스</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1877</v>
+        <v>3985</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-10.62%</t>
+          <t>'-5.01%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.28</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="F16" t="n">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="G16" t="n">
-        <v>106</v>
+        <v>188</v>
       </c>
       <c r="H16" t="n">
-        <v>5.35</v>
+        <v>2.2</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>2100</v>
+        <v>4195</v>
       </c>
       <c r="K16" t="n">
-        <v>2120</v>
+        <v>4280</v>
       </c>
       <c r="L16" t="n">
-        <v>2130</v>
+        <v>4480</v>
       </c>
       <c r="M16" t="n">
-        <v>1846</v>
+        <v>3915</v>
       </c>
       <c r="N16" t="n">
-        <v>5.07</v>
+        <v>1.2</v>
       </c>
       <c r="O16" t="n">
-        <v>9022070103</v>
+        <v>145296482989</v>
       </c>
       <c r="P16" t="n">
-        <v>4980</v>
+        <v>8100</v>
       </c>
       <c r="Q16" t="n">
-        <v>810</v>
+        <v>592</v>
       </c>
       <c r="R16" t="n">
-        <v>38000</v>
+        <v>-347000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>세계 최초 고방사 세라믹 코팅 로봇 개발 및 100억 국책 프로젝트 선정 관련 내용. 주가 하락 및 부정적 전망이 우세.</t>
+          <t>광통신 섹터의 강세와 루멘텀의 폭등에 따른 기대감 언급. 단기 차익 실현 움직임도 관찰됨.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['로봇', '국책 프로젝트', '세라믹 코팅']</t>
+          <t>['광통신', '루멘텀', '5G 상용화']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,90 +1936,90 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>138360</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>54100</v>
+        <v>17390</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-11.89%</t>
+          <t>'-9.47%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.02</v>
+        <v>-0.46</v>
       </c>
       <c r="E17" t="n">
-        <v>458</v>
+        <v>119</v>
       </c>
       <c r="F17" t="n">
-        <v>330</v>
+        <v>45</v>
       </c>
       <c r="G17" t="n">
-        <v>1266</v>
+        <v>82</v>
       </c>
       <c r="H17" t="n">
-        <v>22.34</v>
+        <v>0.65</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>61400</v>
+        <v>19210</v>
       </c>
       <c r="K17" t="n">
-        <v>60600</v>
+        <v>19010</v>
       </c>
       <c r="L17" t="n">
-        <v>60800</v>
+        <v>19840</v>
       </c>
       <c r="M17" t="n">
-        <v>53400</v>
+        <v>17200</v>
       </c>
       <c r="N17" t="n">
-        <v>22.32</v>
+        <v>1.11</v>
       </c>
       <c r="O17" t="n">
-        <v>157302755100</v>
+        <v>74535985940</v>
       </c>
       <c r="P17" t="n">
-        <v>139200</v>
+        <v>28800</v>
       </c>
       <c r="Q17" t="n">
-        <v>53400</v>
+        <v>11550</v>
       </c>
       <c r="R17" t="n">
-        <v>-351000</v>
+        <v>7000</v>
       </c>
       <c r="S17" t="n">
-        <v>-92000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>체코 원전 시공 계약 불발 및 국내 건설사 관련 논란. 정치적 이슈와 연관된 부정적 전망.</t>
+          <t>보호 예수 물량 출회 및 반도체 섹터 조정에 따른 주가 하락 불가피 전망. 투자 주의 및 도망 권고.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['체코 원전', '시공 계약', '이재명']</t>
+          <t>['보호 예수', '반도체', '주가 하락']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10950</v>
+        <v>55000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-23.27%</t>
+          <t>'-10.42%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.23</v>
+        <v>0.02</v>
       </c>
       <c r="E18" t="n">
-        <v>340</v>
+        <v>529</v>
       </c>
       <c r="F18" t="n">
-        <v>210</v>
+        <v>375</v>
       </c>
       <c r="G18" t="n">
-        <v>687</v>
+        <v>1449</v>
       </c>
       <c r="H18" t="n">
-        <v>9.6</v>
+        <v>22.34</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,58 +2067,334 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>14270</v>
+        <v>61400</v>
       </c>
       <c r="K18" t="n">
-        <v>14180</v>
+        <v>60600</v>
       </c>
       <c r="L18" t="n">
-        <v>14180</v>
+        <v>60800</v>
       </c>
       <c r="M18" t="n">
-        <v>10940</v>
+        <v>53400</v>
       </c>
       <c r="N18" t="n">
-        <v>9.83</v>
+        <v>22.32</v>
       </c>
       <c r="O18" t="n">
-        <v>168056755355</v>
+        <v>182673148100</v>
       </c>
       <c r="P18" t="n">
-        <v>40350</v>
+        <v>139200</v>
       </c>
       <c r="Q18" t="n">
-        <v>3320</v>
+        <v>53400</v>
       </c>
       <c r="R18" t="n">
-        <v>-653000</v>
+        <v>-351000</v>
       </c>
       <c r="S18" t="n">
-        <v>-79000</v>
+        <v>-92000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>체코 원전 사업 관련 불확실성 증폭 및 목표가 하향 조정. 정부 정책 변화와 공매도 관련 논란.</t>
+          <t>체코 원전 시공사 변경으로 인한 악재 발생. 기자재는 계약 유지.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>['체코 원전', '시공사 변경', '협상 결렬']</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>034020</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>앤로보틱스</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1853</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>'-11.76%</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E19" t="n">
+        <v>50</v>
+      </c>
+      <c r="F19" t="n">
+        <v>32</v>
+      </c>
+      <c r="G19" t="n">
+        <v>122</v>
+      </c>
+      <c r="H19" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>2100</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2120</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2130</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1846</v>
+      </c>
+      <c r="N19" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="O19" t="n">
+        <v>9866973255</v>
+      </c>
+      <c r="P19" t="n">
+        <v>4980</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>810</v>
+      </c>
+      <c r="R19" t="n">
+        <v>38000</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>국책 프로젝트 선정 소식에도 불구하고 부정적인 전망이 우세. 주가 하락 가능성 및 투자 주의 의견.</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>['로봇', '국책 프로젝트', '주가 흐름']</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>138360</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>삼기에너지솔루션즈</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2235</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>'-13.04%</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="E20" t="n">
+        <v>43</v>
+      </c>
+      <c r="F20" t="n">
+        <v>34</v>
+      </c>
+      <c r="G20" t="n">
+        <v>65</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>2570</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2500</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2575</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2225</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="O20" t="n">
+        <v>11114200574</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2965</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>865</v>
+      </c>
+      <c r="R20" t="n">
+        <v>143000</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-149000</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>전환사채 발행 물량 출회 및 주가 하락에 대한 우려. 매물 폭탄 가능성 및 하한가 예상.</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="n">
         <v>0.1</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>['체코 원전', '목표가 하향', '공매도']</t>
-        </is>
-      </c>
-      <c r="X18" t="n">
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>['전환사채', '매물 폭탄', '주가 하락']</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>419050</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>11390</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>'-20.18%</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="E21" t="n">
+        <v>408</v>
+      </c>
+      <c r="F21" t="n">
+        <v>239</v>
+      </c>
+      <c r="G21" t="n">
+        <v>802</v>
+      </c>
+      <c r="H21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>14270</v>
+      </c>
+      <c r="K21" t="n">
+        <v>14180</v>
+      </c>
+      <c r="L21" t="n">
+        <v>14180</v>
+      </c>
+      <c r="M21" t="n">
+        <v>10930</v>
+      </c>
+      <c r="N21" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="O21" t="n">
+        <v>187336529855</v>
+      </c>
+      <c r="P21" t="n">
+        <v>40350</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3320</v>
+      </c>
+      <c r="R21" t="n">
+        <v>-653000</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-79000</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>체코 원전 사업 관련 불확실성으로 인한 주가 하락. 단기 악재 및 과매도 구간 진입.</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>['체코 원전', '과매도', '단기 악재']</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
         <v>20</v>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>047040</t>
         </is>

--- a/data/trending_integrated_20261029_10.xlsx
+++ b/data/trending_integrated_20261029_10.xlsx
@@ -567,21 +567,21 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4910</v>
+        <v>4805</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+24.78%</t>
+          <t>'+22.11%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.4</v>
       </c>
       <c r="E2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G2" t="n">
         <v>28</v>
@@ -610,7 +610,7 @@
         <v>1.02</v>
       </c>
       <c r="O2" t="n">
-        <v>5520129143</v>
+        <v>5640735648</v>
       </c>
       <c r="P2" t="n">
         <v>10200</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>부품 수주 및 PO 임박으로 인한 10배 상승 기대감. 실제 납품 사실 기반.</t>
+          <t>아틀라스 부품 수주 및 양산 준비에 따른 주가 급등 기대감. 타사 비교 우위.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['부품 수주', 'PO', '10배 상승']</t>
+          <t>['아틀라스', '부품수주', 'PO']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,11 +659,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9450</v>
+        <v>9310</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+18.27%</t>
+          <t>'+16.52%</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -676,7 +676,7 @@
         <v>54</v>
       </c>
       <c r="G3" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H3" t="n">
         <v>17.97</v>
@@ -702,7 +702,7 @@
         <v>18.64</v>
       </c>
       <c r="O3" t="n">
-        <v>103238896215</v>
+        <v>105808051885</v>
       </c>
       <c r="P3" t="n">
         <v>22450</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 광통신 업체 폭등에 따른 기대감. LED 광원 관련 경쟁사 언급.</t>
+          <t>광통신 섹터 내 일부 종목 상승과 함께 광전자 주가 상승 기대감. 차트 기반 분석.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['LED 광원', '광통신', '호재']</t>
+          <t>['광통신', '차트', '섹터']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>37900</v>
+        <v>37300</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+8.91%</t>
+          <t>'+7.18%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -794,7 +794,7 @@
         <v>6.54</v>
       </c>
       <c r="O4" t="n">
-        <v>82740659725</v>
+        <v>87301741225</v>
       </c>
       <c r="P4" t="n">
         <v>126600</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8085</v>
+        <v>7960</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+8.52%</t>
+          <t>'+6.85%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-1.04</v>
       </c>
       <c r="E5" t="n">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="F5" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="G5" t="n">
-        <v>173</v>
+        <v>189</v>
       </c>
       <c r="H5" t="n">
         <v>0.42</v>
@@ -886,7 +886,7 @@
         <v>1.46</v>
       </c>
       <c r="O5" t="n">
-        <v>87371389800</v>
+        <v>90045334920</v>
       </c>
       <c r="P5" t="n">
         <v>10300</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>주가 상승과 하락에 대한 상반된 의견이 존재. 투자자들의 관망세 및 매도 의견이 혼재.</t>
+          <t>하이닉스 물량 완판 및 반도체 시장 속도전 돌입. 외인 매수세 유입으로 인한 상승 기대감.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['반도체', '대장주', '대량거래']</t>
+          <t>['반도체', '외인매수', '완판']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14740</v>
+        <v>14730</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+2.43%</t>
+          <t>'+2.36%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.06</v>
       </c>
       <c r="E6" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F6" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G6" t="n">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="H6" t="n">
         <v>8.050000000000001</v>
@@ -978,7 +978,7 @@
         <v>8.109999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>41278362625</v>
+        <v>42278568070</v>
       </c>
       <c r="P6" t="n">
         <v>49800</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>의료 AI 섹터의 강세 및 긍정적인 차트 분석. 공매도 세력과의 경쟁 및 숏스퀴즈 기대감.</t>
+          <t>미국 의료 AI 섹터 동반 상승 및 ESMO 2026 스코프 기대감. 3분기 실적 발표 대기.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['의료 AI', '숏스퀴즈', '차트 분석']</t>
+          <t>['의료AI', 'ESMO', '실적발표']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1508000</v>
+        <v>1500000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+1.41%</t>
+          <t>'+0.87%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="G7" t="n">
-        <v>1572</v>
+        <v>1512</v>
       </c>
       <c r="H7" t="n">
         <v>48.66</v>
@@ -1064,13 +1064,13 @@
         <v>1587000</v>
       </c>
       <c r="M7" t="n">
-        <v>1501000</v>
+        <v>1495000</v>
       </c>
       <c r="N7" t="n">
         <v>48.61</v>
       </c>
       <c r="O7" t="n">
-        <v>2811864059500</v>
+        <v>3099747762500</v>
       </c>
       <c r="P7" t="n">
         <v>2987000</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>주가 상승 추세 지속 및 200만원 돌파 기대감. 경쟁사 대비 우수한 주주환원 정책.</t>
+          <t>SK하이닉스 주가 상승 추세 지속 전망. 자사주 매입 및 견조한 실적 기반.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['자사주 매입', '주주환원', '대장주']</t>
+          <t>['SK하이닉스', '자사주매입', '실적']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>64300</v>
+        <v>63700</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.16%</t>
+          <t>'-0.78%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.54</v>
       </c>
       <c r="E8" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F8" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G8" t="n">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="H8" t="n">
         <v>41.55</v>
@@ -1162,7 +1162,7 @@
         <v>41.01</v>
       </c>
       <c r="O8" t="n">
-        <v>101098272300</v>
+        <v>109918144850</v>
       </c>
       <c r="P8" t="n">
         <v>67300</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>수주 공시 및 신고가 도전 기대감. 자사주 매입 지속 및 반도체 투자 확대 수혜.</t>
+          <t>수주 공시 및 신고가 도전 기대감. 자사주 매입 지속 및 건설 섹터 내 상승세.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['수주 공시', '신고가', '자사주 매입']</t>
+          <t>['수주공시', '자사주매입', '신고가']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,83 +1207,83 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>187000</v>
+        <v>14620</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.63%</t>
+          <t>'-2.40%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.1</v>
+        <v>0.46</v>
       </c>
       <c r="E9" t="n">
+        <v>108</v>
+      </c>
+      <c r="F9" t="n">
         <v>68</v>
       </c>
-      <c r="F9" t="n">
-        <v>47</v>
-      </c>
       <c r="G9" t="n">
-        <v>154</v>
+        <v>571</v>
       </c>
       <c r="H9" t="n">
-        <v>75</v>
+        <v>3.33</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>190100</v>
+        <v>14980</v>
       </c>
       <c r="K9" t="n">
-        <v>189400</v>
+        <v>15120</v>
       </c>
       <c r="L9" t="n">
-        <v>197000</v>
+        <v>15950</v>
       </c>
       <c r="M9" t="n">
-        <v>185900</v>
+        <v>14600</v>
       </c>
       <c r="N9" t="n">
-        <v>74.90000000000001</v>
+        <v>2.87</v>
       </c>
       <c r="O9" t="n">
-        <v>751467630900</v>
+        <v>119607642825</v>
       </c>
       <c r="P9" t="n">
-        <v>243500</v>
+        <v>31500</v>
       </c>
       <c r="Q9" t="n">
-        <v>71000</v>
+        <v>1819</v>
       </c>
       <c r="R9" t="n">
-        <v>-484000</v>
+        <v>-213000</v>
       </c>
       <c r="S9" t="n">
-        <v>-1000</v>
+        <v>41000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>우선주 소각 논의 및 주주환원 정책 지연에 대한 실망감.</t>
+          <t>메타 관련 뉴스 및 3분기 실적 전망. 루멘텀 인수설 및 반도체 공정용 레이저 히터 특허 등록.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['우선주 소각', '주주환원', '기관 매도']</t>
+          <t>['메타', '실적전망', '특허']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>523000</v>
+        <v>517000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.06%</t>
+          <t>'-3.18%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.08</v>
       </c>
       <c r="E10" t="n">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="F10" t="n">
         <v>118</v>
       </c>
       <c r="G10" t="n">
-        <v>914</v>
+        <v>954</v>
       </c>
       <c r="H10" t="n">
         <v>24.78</v>
@@ -1340,13 +1340,13 @@
         <v>563000</v>
       </c>
       <c r="M10" t="n">
-        <v>520000</v>
+        <v>517000</v>
       </c>
       <c r="N10" t="n">
         <v>24.86</v>
       </c>
       <c r="O10" t="n">
-        <v>305374487500</v>
+        <v>320116859500</v>
       </c>
       <c r="P10" t="n">
         <v>723000</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>컨센서스를 상회하는 호실적 발표 및 흑자 전환. ESS, 전고체 관련주로서 긍정적인 전망 제시.</t>
+          <t>컨퍼런스콜 통한 26년 3분기 영업이익 컨센서스 상회. ESS 및 전고체 관련주 급등 기대.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['실적', '컨퍼런스콜', 'ESS']</t>
+          <t>['컨퍼런스콜', '영업이익', '전고체']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,70 +1391,70 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14660</v>
+        <v>25850</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-2.14%</t>
+          <t>'-3.18%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.46</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>105</v>
+        <v>47</v>
       </c>
       <c r="F11" t="n">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="G11" t="n">
-        <v>552</v>
+        <v>157</v>
       </c>
       <c r="H11" t="n">
-        <v>3.33</v>
+        <v>12.23</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>14980</v>
+        <v>26700</v>
       </c>
       <c r="K11" t="n">
-        <v>15120</v>
+        <v>26350</v>
       </c>
       <c r="L11" t="n">
-        <v>15950</v>
+        <v>26350</v>
       </c>
       <c r="M11" t="n">
-        <v>14600</v>
+        <v>25450</v>
       </c>
       <c r="N11" t="n">
-        <v>2.87</v>
+        <v>12.3</v>
       </c>
       <c r="O11" t="n">
-        <v>116668059850</v>
+        <v>22714314650</v>
       </c>
       <c r="P11" t="n">
-        <v>31500</v>
+        <v>59300</v>
       </c>
       <c r="Q11" t="n">
-        <v>1819</v>
+        <v>22000</v>
       </c>
       <c r="R11" t="n">
-        <v>-213000</v>
+        <v>-93000</v>
       </c>
       <c r="S11" t="n">
-        <v>41000</v>
+        <v>-12000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>메타버스 관련 뉴스 및 루멘텀 급등에 따른 기대감. 연말 목표가 3만 원 제시.</t>
+          <t>실적 발표 앞두고 주가 변동성 확대 예상. 태양광 섹터 전반의 흐름 및 실적 기대감.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['광통신', '루멘텀', '메타버스']</t>
+          <t>['실적발표', '태양광', '변동성']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>009830</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25850</v>
+        <v>15980</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.18%</t>
+          <t>'-3.21%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="E12" t="n">
-        <v>44</v>
+        <v>94</v>
       </c>
       <c r="F12" t="n">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="G12" t="n">
-        <v>146</v>
+        <v>234</v>
       </c>
       <c r="H12" t="n">
-        <v>12.23</v>
+        <v>28.07</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>26700</v>
+        <v>16510</v>
       </c>
       <c r="K12" t="n">
-        <v>26350</v>
+        <v>16380</v>
       </c>
       <c r="L12" t="n">
-        <v>26350</v>
+        <v>16440</v>
       </c>
       <c r="M12" t="n">
-        <v>25450</v>
+        <v>15770</v>
       </c>
       <c r="N12" t="n">
-        <v>12.3</v>
+        <v>28.03</v>
       </c>
       <c r="O12" t="n">
-        <v>22138564600</v>
+        <v>26290648740</v>
       </c>
       <c r="P12" t="n">
-        <v>59300</v>
+        <v>35350</v>
       </c>
       <c r="Q12" t="n">
-        <v>22000</v>
+        <v>15770</v>
       </c>
       <c r="R12" t="n">
-        <v>-93000</v>
+        <v>-348000</v>
       </c>
       <c r="S12" t="n">
-        <v>-12000</v>
+        <v>-70000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>실적 발표 예정인 가운데, 시장의 기대와 우려가 혼재. 3분기 적자 예상 가능성 언급.</t>
+          <t>신저점 갱신 및 실적 우려. 향후 전망에 대한 불확실성 증대.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['실적 발표', '태양광', '적자 예상']</t>
+          <t>['신저점', '실적', '전망 불확실']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>009830</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8860</v>
+        <v>182900</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.49%</t>
+          <t>'-3.79%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.37</v>
+        <v>0.1</v>
       </c>
       <c r="E13" t="n">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="F13" t="n">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="G13" t="n">
-        <v>114</v>
+        <v>161</v>
       </c>
       <c r="H13" t="n">
-        <v>0.37</v>
+        <v>75</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>9180</v>
+        <v>190100</v>
       </c>
       <c r="K13" t="n">
-        <v>9200</v>
+        <v>189400</v>
       </c>
       <c r="L13" t="n">
-        <v>10900</v>
+        <v>197000</v>
       </c>
       <c r="M13" t="n">
-        <v>8730</v>
+        <v>182100</v>
       </c>
       <c r="N13" t="n">
-        <v>0.74</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>27612752875</v>
+        <v>815880838250</v>
       </c>
       <c r="P13" t="n">
-        <v>19380</v>
+        <v>243500</v>
       </c>
       <c r="Q13" t="n">
-        <v>3200</v>
+        <v>71000</v>
       </c>
       <c r="R13" t="n">
-        <v>-32000</v>
+        <v>-484000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>주가 조작 의혹 및 외인 매도에 대한 불신. 정상적이지 않은 종목으로 인식.</t>
+          <t>우선주 소각 및 주주환원 정책에 대한 불확실성으로 인한 주가 하락 우려. 기관 매도세.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['주가 조작', '외인 매도', '잡주']</t>
+          <t>['우선주', '주주환원', '소각']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15930</v>
+        <v>8820</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.51%</t>
+          <t>'-3.92%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.04</v>
+        <v>-0.37</v>
       </c>
       <c r="E14" t="n">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c r="F14" t="n">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="G14" t="n">
-        <v>229</v>
+        <v>120</v>
       </c>
       <c r="H14" t="n">
-        <v>28.07</v>
+        <v>0.37</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,38 +1699,38 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>16510</v>
+        <v>9180</v>
       </c>
       <c r="K14" t="n">
-        <v>16380</v>
+        <v>9200</v>
       </c>
       <c r="L14" t="n">
-        <v>16440</v>
+        <v>10900</v>
       </c>
       <c r="M14" t="n">
-        <v>15770</v>
+        <v>8730</v>
       </c>
       <c r="N14" t="n">
-        <v>28.03</v>
+        <v>0.74</v>
       </c>
       <c r="O14" t="n">
-        <v>24196521085</v>
+        <v>27918196005</v>
       </c>
       <c r="P14" t="n">
-        <v>35350</v>
+        <v>19380</v>
       </c>
       <c r="Q14" t="n">
-        <v>15770</v>
+        <v>3200</v>
       </c>
       <c r="R14" t="n">
-        <v>-348000</v>
+        <v>-32000</v>
       </c>
       <c r="S14" t="n">
-        <v>-70000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>신저점 갱신 및 실적 우려. 향후 전망에 대한 불확실성 증대.</t>
+          <t>주가 조작 및 투명성 부족에 대한 강한 불만. 외인 매도세 확인.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,11 +1739,11 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['신저점', '실적', '전망 불확실']</t>
+          <t>['주가조작', '외인매도', '투명성']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>232500</v>
+        <v>230500</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.93%</t>
+          <t>'-4.75%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1777,10 +1777,10 @@
         <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>587</v>
+        <v>608</v>
       </c>
       <c r="G15" t="n">
-        <v>2157</v>
+        <v>2227</v>
       </c>
       <c r="H15" t="n">
         <v>46.19</v>
@@ -1800,13 +1800,13 @@
         <v>249000</v>
       </c>
       <c r="M15" t="n">
-        <v>232000</v>
+        <v>230000</v>
       </c>
       <c r="N15" t="n">
         <v>46.15</v>
       </c>
       <c r="O15" t="n">
-        <v>2510060323000</v>
+        <v>2730071128750</v>
       </c>
       <c r="P15" t="n">
         <v>374500</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>주주환원 정책 지연 및 미흡에 대한 강한 불만. 경쟁사 대비 저조한 성과.</t>
+          <t>주주환원 정책에 대한 불만 고조 및 실적 대비 낮은 주가 부양에 대한 비판.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['주주환원', '성과급', '대국민 사기']</t>
+          <t>['주주환원', '실적', '주가부양']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3985</v>
+        <v>3935</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-5.01%</t>
+          <t>'-6.20%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F16" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G16" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H16" t="n">
         <v>2.2</v>
@@ -1898,7 +1898,7 @@
         <v>1.2</v>
       </c>
       <c r="O16" t="n">
-        <v>145296482989</v>
+        <v>147430455897</v>
       </c>
       <c r="P16" t="n">
         <v>8100</v>
@@ -1943,83 +1943,83 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17390</v>
+        <v>55000</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-9.47%</t>
+          <t>'-10.42%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.46</v>
+        <v>0.02</v>
       </c>
       <c r="E17" t="n">
-        <v>119</v>
+        <v>567</v>
       </c>
       <c r="F17" t="n">
-        <v>45</v>
+        <v>400</v>
       </c>
       <c r="G17" t="n">
-        <v>82</v>
+        <v>1588</v>
       </c>
       <c r="H17" t="n">
-        <v>0.65</v>
+        <v>22.34</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>19210</v>
+        <v>61400</v>
       </c>
       <c r="K17" t="n">
-        <v>19010</v>
+        <v>60600</v>
       </c>
       <c r="L17" t="n">
-        <v>19840</v>
+        <v>60800</v>
       </c>
       <c r="M17" t="n">
-        <v>17200</v>
+        <v>53400</v>
       </c>
       <c r="N17" t="n">
-        <v>1.11</v>
+        <v>22.32</v>
       </c>
       <c r="O17" t="n">
-        <v>74535985940</v>
+        <v>196076961550</v>
       </c>
       <c r="P17" t="n">
-        <v>28800</v>
+        <v>139200</v>
       </c>
       <c r="Q17" t="n">
-        <v>11550</v>
+        <v>53400</v>
       </c>
       <c r="R17" t="n">
-        <v>7000</v>
+        <v>-351000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-92000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>보호 예수 물량 출회 및 반도체 섹터 조정에 따른 주가 하락 불가피 전망. 투자 주의 및 도망 권고.</t>
+          <t>체코 원전 사업 시공사 변경 관련 불확실성으로 인한 주가 하락. 공매도 및 정치적 이슈 연관.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['보호 예수', '반도체', '주가 하락']</t>
+          <t>['체코원전', '시공사', '공매도']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,90 +2028,90 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>55000</v>
+        <v>17110</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-10.42%</t>
+          <t>'-10.93%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.02</v>
+        <v>-0.46</v>
       </c>
       <c r="E18" t="n">
-        <v>529</v>
+        <v>118</v>
       </c>
       <c r="F18" t="n">
-        <v>375</v>
+        <v>44</v>
       </c>
       <c r="G18" t="n">
-        <v>1449</v>
+        <v>89</v>
       </c>
       <c r="H18" t="n">
-        <v>22.34</v>
+        <v>0.65</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>61400</v>
+        <v>19210</v>
       </c>
       <c r="K18" t="n">
-        <v>60600</v>
+        <v>19010</v>
       </c>
       <c r="L18" t="n">
-        <v>60800</v>
+        <v>19840</v>
       </c>
       <c r="M18" t="n">
-        <v>53400</v>
+        <v>17110</v>
       </c>
       <c r="N18" t="n">
-        <v>22.32</v>
+        <v>1.11</v>
       </c>
       <c r="O18" t="n">
-        <v>182673148100</v>
+        <v>75987598090</v>
       </c>
       <c r="P18" t="n">
-        <v>139200</v>
+        <v>28800</v>
       </c>
       <c r="Q18" t="n">
-        <v>53400</v>
+        <v>11550</v>
       </c>
       <c r="R18" t="n">
-        <v>-351000</v>
+        <v>7000</v>
       </c>
       <c r="S18" t="n">
-        <v>-92000</v>
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>체코 원전 시공사 변경으로 인한 악재 발생. 기자재는 계약 유지.</t>
+          <t>보호 예수 물량 출회 및 반도체 섹터 하락 영향. 투자자들의 대규모 손실 우려.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['체코 원전', '시공사 변경', '협상 결렬']</t>
+          <t>['보호예수', '반도체하락', '개미탕']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1853</v>
+        <v>1861</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-11.76%</t>
+          <t>'-11.38%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.28</v>
       </c>
       <c r="E19" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F19" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G19" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="H19" t="n">
         <v>5.35</v>
@@ -2174,7 +2174,7 @@
         <v>5.07</v>
       </c>
       <c r="O19" t="n">
-        <v>9866973255</v>
+        <v>10068734818</v>
       </c>
       <c r="P19" t="n">
         <v>4980</v>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2235</v>
+        <v>2220</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-13.04%</t>
+          <t>'-13.62%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.47</v>
       </c>
       <c r="E20" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F20" t="n">
         <v>34</v>
       </c>
       <c r="G20" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H20" t="n">
         <v>1.22</v>
@@ -2260,13 +2260,13 @@
         <v>2575</v>
       </c>
       <c r="M20" t="n">
-        <v>2225</v>
+        <v>2215</v>
       </c>
       <c r="N20" t="n">
         <v>1.69</v>
       </c>
       <c r="O20" t="n">
-        <v>11114200574</v>
+        <v>11586541369</v>
       </c>
       <c r="P20" t="n">
         <v>2965</v>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>전환사채 발행 물량 출회 및 주가 하락에 대한 우려. 매물 폭탄 가능성 및 하한가 예상.</t>
+          <t>전환사채 관련 물량 출회 우려 및 주가 급락. 실적과 무관한 주가 흐름에 대한 불만.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['전환사채', '매물 폭탄', '주가 하락']</t>
+          <t>['전환사채', '매물폭탄', '주가급락']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11390</v>
+        <v>11530</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-20.18%</t>
+          <t>'-19.20%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>-0.23</v>
       </c>
       <c r="E21" t="n">
-        <v>408</v>
+        <v>452</v>
       </c>
       <c r="F21" t="n">
-        <v>239</v>
+        <v>261</v>
       </c>
       <c r="G21" t="n">
-        <v>802</v>
+        <v>914</v>
       </c>
       <c r="H21" t="n">
         <v>9.6</v>
@@ -2358,7 +2358,7 @@
         <v>9.83</v>
       </c>
       <c r="O21" t="n">
-        <v>187336529855</v>
+        <v>206494220385</v>
       </c>
       <c r="P21" t="n">
         <v>40350</v>
@@ -2374,16 +2374,16 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>체코 원전 사업 관련 불확실성으로 인한 주가 하락. 단기 악재 및 과매도 구간 진입.</t>
+          <t>체코 원전 관련 불확실성으로 인한 목표가 하향 및 주가 하락 전망. 공매도 관련 논란.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['체코 원전', '과매도', '단기 악재']</t>
+          <t>['체코원전', '공매도', '목표가']</t>
         </is>
       </c>
       <c r="X21" t="n">

--- a/data/trending_integrated_20261029_10.xlsx
+++ b/data/trending_integrated_20261029_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z21"/>
+  <dimension ref="A1:Z22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,21 +567,21 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4805</v>
+        <v>4820</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+22.11%</t>
+          <t>'+22.49%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.4</v>
       </c>
       <c r="E2" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G2" t="n">
         <v>28</v>
@@ -610,7 +610,7 @@
         <v>1.02</v>
       </c>
       <c r="O2" t="n">
-        <v>5640735648</v>
+        <v>5807470868</v>
       </c>
       <c r="P2" t="n">
         <v>10200</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>아틀라스 부품 수주 및 양산 준비에 따른 주가 급등 기대감. 타사 비교 우위.</t>
+          <t>아틀라스 부품 공급망 관련 긍정적 뉴스 및 수주 기대감으로 인한 급등 전망.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['아틀라스', '부품수주', 'PO']</t>
+          <t>['씨티알모빌리티', '아틀라스', '부품 수주']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,21 +659,21 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9310</v>
+        <v>9300</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.52%</t>
+          <t>'+16.40%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.67</v>
       </c>
       <c r="E3" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F3" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G3" t="n">
         <v>49</v>
@@ -702,7 +702,7 @@
         <v>18.64</v>
       </c>
       <c r="O3" t="n">
-        <v>105808051885</v>
+        <v>108196191570</v>
       </c>
       <c r="P3" t="n">
         <v>22450</v>
@@ -751,21 +751,21 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>37300</v>
+        <v>37400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+7.18%</t>
+          <t>'+7.47%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.74</v>
       </c>
       <c r="E4" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F4" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G4" t="n">
         <v>123</v>
@@ -794,7 +794,7 @@
         <v>6.54</v>
       </c>
       <c r="O4" t="n">
-        <v>87301741225</v>
+        <v>89330152450</v>
       </c>
       <c r="P4" t="n">
         <v>126600</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7960</v>
+        <v>7930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+6.85%</t>
+          <t>'+6.44%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-1.04</v>
       </c>
       <c r="E5" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="F5" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G5" t="n">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H5" t="n">
         <v>0.42</v>
@@ -886,7 +886,7 @@
         <v>1.46</v>
       </c>
       <c r="O5" t="n">
-        <v>90045334920</v>
+        <v>91734271935</v>
       </c>
       <c r="P5" t="n">
         <v>10300</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>하이닉스 물량 완판 및 반도체 시장 속도전 돌입. 외인 매수세 유입으로 인한 상승 기대감.</t>
+          <t>하이닉스 물량 완판 및 광주반도체 관련 언급. 외인 매수세에 대한 긍정적 기대감 존재.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['반도체', '외인매수', '완판']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14730</v>
+        <v>14750</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+2.36%</t>
+          <t>'+2.50%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.06</v>
       </c>
       <c r="E6" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G6" t="n">
-        <v>231</v>
+        <v>257</v>
       </c>
       <c r="H6" t="n">
         <v>8.050000000000001</v>
@@ -978,7 +978,7 @@
         <v>8.109999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>42278568070</v>
+        <v>43193585785</v>
       </c>
       <c r="P6" t="n">
         <v>49800</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>미국 의료 AI 섹터 동반 상승 및 ESMO 2026 스코프 기대감. 3분기 실적 발표 대기.</t>
+          <t>미국 의료 AI 섹터 급등 및 템퍼스AI 관련 언급. 공매도 세력에 대한 공격적인 심리 표현.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['의료AI', 'ESMO', '실적발표']</t>
+          <t>['의료AI', '공매도']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="G7" t="n">
-        <v>1512</v>
+        <v>1407</v>
       </c>
       <c r="H7" t="n">
         <v>48.66</v>
@@ -1064,13 +1064,13 @@
         <v>1587000</v>
       </c>
       <c r="M7" t="n">
-        <v>1495000</v>
+        <v>1493000</v>
       </c>
       <c r="N7" t="n">
         <v>48.61</v>
       </c>
       <c r="O7" t="n">
-        <v>3099747762500</v>
+        <v>3316253166000</v>
       </c>
       <c r="P7" t="n">
         <v>2987000</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>SK하이닉스 주가 상승 추세 지속 전망. 자사주 매입 및 견조한 실적 기반.</t>
+          <t>주주환원 정책 호조와 실적 개선 기대감으로 인한 긍정적 주가 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['SK하이닉스', '자사주매입', '실적']</t>
+          <t>['SK하이닉스', '주주환원', '실적']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,83 +1115,83 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>63700</v>
+        <v>28650</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-0.78%</t>
+          <t>'-0.17%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.54</v>
+        <v>0.04</v>
       </c>
       <c r="E8" t="n">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="F8" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="G8" t="n">
-        <v>366</v>
+        <v>58</v>
       </c>
       <c r="H8" t="n">
-        <v>41.55</v>
+        <v>1.77</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>64200</v>
+        <v>28700</v>
       </c>
       <c r="K8" t="n">
-        <v>64200</v>
+        <v>29150</v>
       </c>
       <c r="L8" t="n">
-        <v>65500</v>
+        <v>31400</v>
       </c>
       <c r="M8" t="n">
-        <v>62500</v>
+        <v>28350</v>
       </c>
       <c r="N8" t="n">
-        <v>41.01</v>
+        <v>1.73</v>
       </c>
       <c r="O8" t="n">
-        <v>109918144850</v>
+        <v>84195679575</v>
       </c>
       <c r="P8" t="n">
-        <v>67300</v>
+        <v>59600</v>
       </c>
       <c r="Q8" t="n">
-        <v>23150</v>
+        <v>1850</v>
       </c>
       <c r="R8" t="n">
-        <v>271000</v>
+        <v>-42000</v>
       </c>
       <c r="S8" t="n">
-        <v>-21000</v>
+        <v>11000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>수주 공시 및 신고가 도전 기대감. 자사주 매입 지속 및 건설 섹터 내 상승세.</t>
+          <t>루멘텀홀딩스 인수 관련 호재 및 기관 매수세 언급. 광통신주 동반 하락으로 인한 관망세.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['수주공시', '자사주매입', '신고가']</t>
+          <t>['루멘텀', '기관']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,77 +1200,77 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>043260</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14620</v>
+        <v>63400</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.40%</t>
+          <t>'-1.25%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.46</v>
+        <v>0.54</v>
       </c>
       <c r="E9" t="n">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="F9" t="n">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="G9" t="n">
-        <v>571</v>
+        <v>381</v>
       </c>
       <c r="H9" t="n">
-        <v>3.33</v>
+        <v>41.55</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>14980</v>
+        <v>64200</v>
       </c>
       <c r="K9" t="n">
-        <v>15120</v>
+        <v>64200</v>
       </c>
       <c r="L9" t="n">
-        <v>15950</v>
+        <v>65500</v>
       </c>
       <c r="M9" t="n">
-        <v>14600</v>
+        <v>62500</v>
       </c>
       <c r="N9" t="n">
-        <v>2.87</v>
+        <v>41.01</v>
       </c>
       <c r="O9" t="n">
-        <v>119607642825</v>
+        <v>113927230000</v>
       </c>
       <c r="P9" t="n">
-        <v>31500</v>
+        <v>67300</v>
       </c>
       <c r="Q9" t="n">
-        <v>1819</v>
+        <v>23150</v>
       </c>
       <c r="R9" t="n">
-        <v>-213000</v>
+        <v>271000</v>
       </c>
       <c r="S9" t="n">
-        <v>41000</v>
+        <v>-21000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>메타 관련 뉴스 및 3분기 실적 전망. 루멘텀 인수설 및 반도체 공정용 레이저 히터 특허 등록.</t>
+          <t>수주 공시 및 자사주 매입 소각 예정에 따른 신고가 경신 기대감.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['메타', '실적전망', '특허']</t>
+          <t>['삼성E&amp;A', '수주공시', '자사주소각']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>517000</v>
+        <v>14670</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-3.18%</t>
+          <t>'-2.07%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.08</v>
+        <v>0.46</v>
       </c>
       <c r="E10" t="n">
-        <v>220</v>
+        <v>112</v>
       </c>
       <c r="F10" t="n">
-        <v>118</v>
+        <v>69</v>
       </c>
       <c r="G10" t="n">
-        <v>954</v>
+        <v>618</v>
       </c>
       <c r="H10" t="n">
-        <v>24.78</v>
+        <v>3.33</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>534000</v>
+        <v>14980</v>
       </c>
       <c r="K10" t="n">
-        <v>546000</v>
+        <v>15120</v>
       </c>
       <c r="L10" t="n">
-        <v>563000</v>
+        <v>15950</v>
       </c>
       <c r="M10" t="n">
-        <v>517000</v>
+        <v>14600</v>
       </c>
       <c r="N10" t="n">
-        <v>24.86</v>
+        <v>2.87</v>
       </c>
       <c r="O10" t="n">
-        <v>320116859500</v>
+        <v>121681239105</v>
       </c>
       <c r="P10" t="n">
-        <v>723000</v>
+        <v>31500</v>
       </c>
       <c r="Q10" t="n">
-        <v>259000</v>
+        <v>1819</v>
       </c>
       <c r="R10" t="n">
-        <v>6000</v>
+        <v>-213000</v>
       </c>
       <c r="S10" t="n">
-        <v>5000</v>
+        <v>41000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>컨퍼런스콜 통한 26년 3분기 영업이익 컨센서스 상회. ESS 및 전고체 관련주 급등 기대.</t>
+          <t>메타 관련 뉴스 및 3분기 예상 실적 언급. 루멘텀 인수 관련 호재 및 반도체 공정용 레이저 히터 제어 특허 등록 사실 포함.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['컨퍼런스콜', '영업이익', '전고체']</t>
+          <t>['메타', '루멘텀']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>25850</v>
+        <v>520000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.18%</t>
+          <t>'-2.62%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.08</v>
       </c>
       <c r="E11" t="n">
-        <v>47</v>
+        <v>228</v>
       </c>
       <c r="F11" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="G11" t="n">
-        <v>157</v>
+        <v>989</v>
       </c>
       <c r="H11" t="n">
-        <v>12.23</v>
+        <v>24.78</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>26700</v>
+        <v>534000</v>
       </c>
       <c r="K11" t="n">
-        <v>26350</v>
+        <v>546000</v>
       </c>
       <c r="L11" t="n">
-        <v>26350</v>
+        <v>563000</v>
       </c>
       <c r="M11" t="n">
-        <v>25450</v>
+        <v>516000</v>
       </c>
       <c r="N11" t="n">
-        <v>12.3</v>
+        <v>24.86</v>
       </c>
       <c r="O11" t="n">
-        <v>22714314650</v>
+        <v>332653431000</v>
       </c>
       <c r="P11" t="n">
-        <v>59300</v>
+        <v>723000</v>
       </c>
       <c r="Q11" t="n">
-        <v>22000</v>
+        <v>259000</v>
       </c>
       <c r="R11" t="n">
-        <v>-93000</v>
+        <v>6000</v>
       </c>
       <c r="S11" t="n">
-        <v>-12000</v>
+        <v>5000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>실적 발표 앞두고 주가 변동성 확대 예상. 태양광 섹터 전반의 흐름 및 실적 기대감.</t>
+          <t>26년 3분기 연결 영업이익 컨센서스 상회 및 호실적 발표. ESS, 전고체 관련주 동반 상승. 긍정적 전망.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['실적발표', '태양광', '변동성']</t>
+          <t>['영업이익', '컨센서스', 'ESS']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>009830</t>
+          <t>006400</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15980</v>
+        <v>184200</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.21%</t>
+          <t>'-3.10%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="E12" t="n">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="F12" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G12" t="n">
-        <v>234</v>
+        <v>214</v>
       </c>
       <c r="H12" t="n">
-        <v>28.07</v>
+        <v>75</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>16510</v>
+        <v>190100</v>
       </c>
       <c r="K12" t="n">
-        <v>16380</v>
+        <v>189400</v>
       </c>
       <c r="L12" t="n">
-        <v>16440</v>
+        <v>197000</v>
       </c>
       <c r="M12" t="n">
-        <v>15770</v>
+        <v>182100</v>
       </c>
       <c r="N12" t="n">
-        <v>28.03</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>26290648740</v>
+        <v>854155574150</v>
       </c>
       <c r="P12" t="n">
-        <v>35350</v>
+        <v>243500</v>
       </c>
       <c r="Q12" t="n">
-        <v>15770</v>
+        <v>71000</v>
       </c>
       <c r="R12" t="n">
-        <v>-348000</v>
+        <v>-484000</v>
       </c>
       <c r="S12" t="n">
-        <v>-70000</v>
+        <v>-1000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>신저점 갱신 및 실적 우려. 향후 전망에 대한 불확실성 증대.</t>
+          <t>주주환원 불확실성과 오너 리스크에 대한 우려.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['신저점', '실적', '전망 불확실']</t>
+          <t>['우선주', '주주환원', '이재용']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>182900</v>
+        <v>15950</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.79%</t>
+          <t>'-3.39%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
       <c r="E13" t="n">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="F13" t="n">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="G13" t="n">
-        <v>161</v>
+        <v>239</v>
       </c>
       <c r="H13" t="n">
-        <v>75</v>
+        <v>28.07</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>190100</v>
+        <v>16510</v>
       </c>
       <c r="K13" t="n">
-        <v>189400</v>
+        <v>16380</v>
       </c>
       <c r="L13" t="n">
-        <v>197000</v>
+        <v>16440</v>
       </c>
       <c r="M13" t="n">
-        <v>182100</v>
+        <v>15770</v>
       </c>
       <c r="N13" t="n">
-        <v>74.90000000000001</v>
+        <v>28.03</v>
       </c>
       <c r="O13" t="n">
-        <v>815880838250</v>
+        <v>27470174790</v>
       </c>
       <c r="P13" t="n">
-        <v>243500</v>
+        <v>35350</v>
       </c>
       <c r="Q13" t="n">
-        <v>71000</v>
+        <v>15770</v>
       </c>
       <c r="R13" t="n">
-        <v>-484000</v>
+        <v>-348000</v>
       </c>
       <c r="S13" t="n">
-        <v>-1000</v>
+        <v>-70000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>우선주 소각 및 주주환원 정책에 대한 불확실성으로 인한 주가 하락 우려. 기관 매도세.</t>
+          <t>실적 부진과 향후 전망에 대한 부정적인 평가.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['우선주', '주주환원', '소각']</t>
+          <t>['삼성중공업', '실적', '조선주']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8820</v>
+        <v>25750</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.92%</t>
+          <t>'-3.56%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.37</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F14" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G14" t="n">
-        <v>120</v>
+        <v>169</v>
       </c>
       <c r="H14" t="n">
-        <v>0.37</v>
+        <v>12.23</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>9180</v>
+        <v>26700</v>
       </c>
       <c r="K14" t="n">
-        <v>9200</v>
+        <v>26350</v>
       </c>
       <c r="L14" t="n">
-        <v>10900</v>
+        <v>26350</v>
       </c>
       <c r="M14" t="n">
-        <v>8730</v>
+        <v>25450</v>
       </c>
       <c r="N14" t="n">
-        <v>0.74</v>
+        <v>12.3</v>
       </c>
       <c r="O14" t="n">
-        <v>27918196005</v>
+        <v>23787009900</v>
       </c>
       <c r="P14" t="n">
-        <v>19380</v>
+        <v>59300</v>
       </c>
       <c r="Q14" t="n">
-        <v>3200</v>
+        <v>22000</v>
       </c>
       <c r="R14" t="n">
-        <v>-32000</v>
+        <v>-93000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-12000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>주가 조작 및 투명성 부족에 대한 강한 불만. 외인 매도세 확인.</t>
+          <t>실적 발표를 앞두고 불확실성이 존재하며, 시장 상황 및 실적 결과에 따른 주가 변동 가능성.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['주가조작', '외인매도', '투명성']</t>
+          <t>['한화솔루션', '실적발표', '태양광']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>009830</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>230500</v>
+        <v>8820</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-4.75%</t>
+          <t>'-3.92%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.04</v>
+        <v>-0.37</v>
       </c>
       <c r="E15" t="n">
-        <v>800</v>
+        <v>49</v>
       </c>
       <c r="F15" t="n">
-        <v>608</v>
+        <v>36</v>
       </c>
       <c r="G15" t="n">
-        <v>2227</v>
+        <v>123</v>
       </c>
       <c r="H15" t="n">
-        <v>46.19</v>
+        <v>0.37</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,38 +1791,38 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>242000</v>
+        <v>9180</v>
       </c>
       <c r="K15" t="n">
-        <v>241000</v>
+        <v>9200</v>
       </c>
       <c r="L15" t="n">
-        <v>249000</v>
+        <v>10900</v>
       </c>
       <c r="M15" t="n">
-        <v>230000</v>
+        <v>8730</v>
       </c>
       <c r="N15" t="n">
-        <v>46.15</v>
+        <v>0.74</v>
       </c>
       <c r="O15" t="n">
-        <v>2730071128750</v>
+        <v>28274519195</v>
       </c>
       <c r="P15" t="n">
-        <v>374500</v>
+        <v>19380</v>
       </c>
       <c r="Q15" t="n">
-        <v>94500</v>
+        <v>3200</v>
       </c>
       <c r="R15" t="n">
-        <v>166000</v>
+        <v>-32000</v>
       </c>
       <c r="S15" t="n">
-        <v>-505000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>주주환원 정책에 대한 불만 고조 및 실적 대비 낮은 주가 부양에 대한 비판.</t>
+          <t>주가 조작 및 투명성 부족에 대한 강한 불만. 외인 매도세 확인.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['주주환원', '실적', '주가부양']</t>
+          <t>['주가조작', '외인매도', '투명성']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,90 +1844,90 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3935</v>
+        <v>230750</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-6.20%</t>
+          <t>'-4.65%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>0.04</v>
       </c>
       <c r="E16" t="n">
-        <v>70</v>
+        <v>800</v>
       </c>
       <c r="F16" t="n">
-        <v>53</v>
+        <v>617</v>
       </c>
       <c r="G16" t="n">
-        <v>189</v>
+        <v>2312</v>
       </c>
       <c r="H16" t="n">
-        <v>2.2</v>
+        <v>46.19</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>4195</v>
+        <v>242000</v>
       </c>
       <c r="K16" t="n">
-        <v>4280</v>
+        <v>241000</v>
       </c>
       <c r="L16" t="n">
-        <v>4480</v>
+        <v>249000</v>
       </c>
       <c r="M16" t="n">
-        <v>3915</v>
+        <v>229000</v>
       </c>
       <c r="N16" t="n">
-        <v>1.2</v>
+        <v>46.15</v>
       </c>
       <c r="O16" t="n">
-        <v>147430455897</v>
+        <v>2967778712000</v>
       </c>
       <c r="P16" t="n">
-        <v>8100</v>
+        <v>374500</v>
       </c>
       <c r="Q16" t="n">
-        <v>592</v>
+        <v>94500</v>
       </c>
       <c r="R16" t="n">
-        <v>-347000</v>
+        <v>166000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-505000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>광통신 섹터의 강세와 루멘텀의 폭등에 따른 기대감 언급. 단기 차익 실현 움직임도 관찰됨.</t>
+          <t>낮은 주주환원 정책에 대한 비판과 실적 대비 부진한 주가 흐름.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['광통신', '루멘텀', '5G 상용화']</t>
+          <t>['주주환원', '영업이익', '삼성전자']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,90 +1936,90 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>55000</v>
+        <v>3960</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-10.42%</t>
+          <t>'-5.60%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.02</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>567</v>
+        <v>74</v>
       </c>
       <c r="F17" t="n">
-        <v>400</v>
+        <v>56</v>
       </c>
       <c r="G17" t="n">
-        <v>1588</v>
+        <v>199</v>
       </c>
       <c r="H17" t="n">
-        <v>22.34</v>
+        <v>2.2</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>61400</v>
+        <v>4195</v>
       </c>
       <c r="K17" t="n">
-        <v>60600</v>
+        <v>4280</v>
       </c>
       <c r="L17" t="n">
-        <v>60800</v>
+        <v>4480</v>
       </c>
       <c r="M17" t="n">
-        <v>53400</v>
+        <v>3915</v>
       </c>
       <c r="N17" t="n">
-        <v>22.32</v>
+        <v>1.2</v>
       </c>
       <c r="O17" t="n">
-        <v>196076961550</v>
+        <v>149207535270</v>
       </c>
       <c r="P17" t="n">
-        <v>139200</v>
+        <v>8100</v>
       </c>
       <c r="Q17" t="n">
-        <v>53400</v>
+        <v>592</v>
       </c>
       <c r="R17" t="n">
-        <v>-351000</v>
+        <v>-347000</v>
       </c>
       <c r="S17" t="n">
-        <v>-92000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>체코 원전 사업 시공사 변경 관련 불확실성으로 인한 주가 하락. 공매도 및 정치적 이슈 연관.</t>
+          <t>광통신 관련 긍정적 뉴스에 따른 기대감과 함께 변동성이 큰 종목.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['체코원전', '시공사', '공매도']</t>
+          <t>['광통신', '루멘텀', '빛과전자']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17110</v>
+        <v>17350</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-10.93%</t>
+          <t>'-9.68%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.46</v>
       </c>
       <c r="E18" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="F18" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G18" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H18" t="n">
         <v>0.65</v>
@@ -2076,13 +2076,13 @@
         <v>19840</v>
       </c>
       <c r="M18" t="n">
-        <v>17110</v>
+        <v>17090</v>
       </c>
       <c r="N18" t="n">
         <v>1.11</v>
       </c>
       <c r="O18" t="n">
-        <v>75987598090</v>
+        <v>77320221280</v>
       </c>
       <c r="P18" t="n">
         <v>28800</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>보호 예수 물량 출회 및 반도체 섹터 하락 영향. 투자자들의 대규모 손실 우려.</t>
+          <t>보호예수 물량 및 대규모 매도 가능성 언급. 반도체 섹터 전반의 하락세 및 주가 폭락 우려.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['보호예수', '반도체하락', '개미탕']</t>
+          <t>['보호예수', '반도체']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1861</v>
+        <v>1878</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-11.38%</t>
+          <t>'-10.57%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2148,7 +2148,7 @@
         <v>34</v>
       </c>
       <c r="G19" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="H19" t="n">
         <v>5.35</v>
@@ -2174,7 +2174,7 @@
         <v>5.07</v>
       </c>
       <c r="O19" t="n">
-        <v>10068734818</v>
+        <v>10723121306</v>
       </c>
       <c r="P19" t="n">
         <v>4980</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>국책 프로젝트 선정 소식에도 불구하고 부정적인 전망이 우세. 주가 하락 가능성 및 투자 주의 의견.</t>
+          <t>세계 최초 고방사 세라믹 코팅 로봇 개발 관련 국책 프로젝트 선정 뉴스 언급. 투자 심리 위축 및 매도세 강한 모습.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['로봇', '국책 프로젝트', '주가 흐름']</t>
+          <t>['로봇', '국책 프로젝트']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2219,83 +2219,83 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>삼기에너지솔루션즈</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2220</v>
+        <v>54900</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-13.62%</t>
+          <t>'-10.59%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.47</v>
+        <v>0.02</v>
       </c>
       <c r="E20" t="n">
-        <v>45</v>
+        <v>598</v>
       </c>
       <c r="F20" t="n">
-        <v>34</v>
+        <v>423</v>
       </c>
       <c r="G20" t="n">
-        <v>70</v>
+        <v>1697</v>
       </c>
       <c r="H20" t="n">
-        <v>1.22</v>
+        <v>22.34</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>2570</v>
+        <v>61400</v>
       </c>
       <c r="K20" t="n">
-        <v>2500</v>
+        <v>60600</v>
       </c>
       <c r="L20" t="n">
-        <v>2575</v>
+        <v>60800</v>
       </c>
       <c r="M20" t="n">
-        <v>2215</v>
+        <v>53400</v>
       </c>
       <c r="N20" t="n">
-        <v>1.69</v>
+        <v>22.32</v>
       </c>
       <c r="O20" t="n">
-        <v>11586541369</v>
+        <v>207427682700</v>
       </c>
       <c r="P20" t="n">
-        <v>2965</v>
+        <v>139200</v>
       </c>
       <c r="Q20" t="n">
-        <v>865</v>
+        <v>53400</v>
       </c>
       <c r="R20" t="n">
-        <v>143000</v>
+        <v>-351000</v>
       </c>
       <c r="S20" t="n">
-        <v>-149000</v>
+        <v>-92000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>전환사채 관련 물량 출회 우려 및 주가 급락. 실적과 무관한 주가 흐름에 대한 불만.</t>
+          <t>체코 원전 사업 관련, 시공사 변경에도 불구하고 두산에너빌리티의 영향은 제한적이라는 분석.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['전환사채', '매물폭탄', '주가급락']</t>
+          <t>['체코 원전', '두산에너빌리티', '시공사']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,97 +2304,189 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>419050</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼기에너지솔루션즈</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11530</v>
+        <v>2220</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-19.20%</t>
+          <t>'-13.62%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.23</v>
+        <v>-0.47</v>
       </c>
       <c r="E21" t="n">
-        <v>452</v>
+        <v>47</v>
       </c>
       <c r="F21" t="n">
-        <v>261</v>
+        <v>35</v>
       </c>
       <c r="G21" t="n">
-        <v>914</v>
+        <v>71</v>
       </c>
       <c r="H21" t="n">
-        <v>9.6</v>
+        <v>1.22</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>14270</v>
+        <v>2570</v>
       </c>
       <c r="K21" t="n">
-        <v>14180</v>
+        <v>2500</v>
       </c>
       <c r="L21" t="n">
-        <v>14180</v>
+        <v>2575</v>
       </c>
       <c r="M21" t="n">
-        <v>10930</v>
+        <v>2205</v>
       </c>
       <c r="N21" t="n">
-        <v>9.83</v>
+        <v>1.69</v>
       </c>
       <c r="O21" t="n">
-        <v>206494220385</v>
+        <v>12026993982</v>
       </c>
       <c r="P21" t="n">
-        <v>40350</v>
+        <v>2965</v>
       </c>
       <c r="Q21" t="n">
-        <v>3320</v>
+        <v>865</v>
       </c>
       <c r="R21" t="n">
-        <v>-653000</v>
+        <v>143000</v>
       </c>
       <c r="S21" t="n">
-        <v>-79000</v>
+        <v>-149000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>체코 원전 관련 불확실성으로 인한 목표가 하향 및 주가 하락 전망. 공매도 관련 논란.</t>
+          <t>전환사채 발행 및 대규모 매물 출회 관련 언급. 주가 하락에 대한 답답함 토로.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['체코원전', '공매도', '목표가']</t>
+          <t>['전환사채', '매물폭탄']</t>
         </is>
       </c>
       <c r="X21" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>419050</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>11370</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>'-20.32%</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="E22" t="n">
+        <v>493</v>
+      </c>
+      <c r="F22" t="n">
+        <v>273</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1077</v>
+      </c>
+      <c r="H22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>14270</v>
+      </c>
+      <c r="K22" t="n">
+        <v>14180</v>
+      </c>
+      <c r="L22" t="n">
+        <v>14180</v>
+      </c>
+      <c r="M22" t="n">
+        <v>10930</v>
+      </c>
+      <c r="N22" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="O22" t="n">
+        <v>216673479785</v>
+      </c>
+      <c r="P22" t="n">
+        <v>40350</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3320</v>
+      </c>
+      <c r="R22" t="n">
+        <v>-653000</v>
+      </c>
+      <c r="S22" t="n">
+        <v>-79000</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>체코 원전 사업 관련 불확실성으로 인한 주가 하락 및 향후 전망 불투명.</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>['체코 원전', '대우건설', '사업 파기']</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
         <v>20</v>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>047040</t>
         </is>

--- a/data/trending_integrated_20261029_10.xlsx
+++ b/data/trending_integrated_20261029_10.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4820</v>
+        <v>4865</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+22.49%</t>
+          <t>'+23.63%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.4</v>
       </c>
       <c r="E2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F2" t="n">
         <v>18</v>
       </c>
       <c r="G2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H2" t="n">
         <v>0.62</v>
@@ -610,7 +610,7 @@
         <v>1.02</v>
       </c>
       <c r="O2" t="n">
-        <v>5807470868</v>
+        <v>5887586813</v>
       </c>
       <c r="P2" t="n">
         <v>10200</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>아틀라스 부품 공급망 관련 긍정적 뉴스 및 수주 기대감으로 인한 급등 전망.</t>
+          <t>부품 공급 계약 임박 및 10배 상승 기대감. 실제 납품 사실과 계양전기 사례 비교. 적자 회사와 차별성 강조.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['씨티알모빌리티', '아틀라스', '부품 수주']</t>
+          <t>['부품 공급', 'PO 임박', '실제 납품']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,21 +659,21 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9300</v>
+        <v>9500</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.40%</t>
+          <t>'+18.90%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.67</v>
       </c>
       <c r="E3" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F3" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G3" t="n">
         <v>49</v>
@@ -702,7 +702,7 @@
         <v>18.64</v>
       </c>
       <c r="O3" t="n">
-        <v>108196191570</v>
+        <v>110977620155</v>
       </c>
       <c r="P3" t="n">
         <v>22450</v>
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>서산</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>37400</v>
+        <v>8070</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+7.47%</t>
+          <t>'+8.32%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.74</v>
+        <v>-1.04</v>
       </c>
       <c r="E4" t="n">
-        <v>48</v>
+        <v>140</v>
       </c>
       <c r="F4" t="n">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="G4" t="n">
-        <v>123</v>
+        <v>226</v>
       </c>
       <c r="H4" t="n">
-        <v>5.8</v>
+        <v>0.42</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,51 +779,51 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>34800</v>
+        <v>7450</v>
       </c>
       <c r="K4" t="n">
-        <v>36600</v>
+        <v>7470</v>
       </c>
       <c r="L4" t="n">
-        <v>40200</v>
+        <v>9680</v>
       </c>
       <c r="M4" t="n">
-        <v>36200</v>
+        <v>7360</v>
       </c>
       <c r="N4" t="n">
-        <v>6.54</v>
+        <v>1.46</v>
       </c>
       <c r="O4" t="n">
-        <v>89330152450</v>
+        <v>93434292040</v>
       </c>
       <c r="P4" t="n">
-        <v>126600</v>
+        <v>10300</v>
       </c>
       <c r="Q4" t="n">
-        <v>15260</v>
+        <v>952</v>
       </c>
       <c r="R4" t="n">
-        <v>52000</v>
+        <v>506000</v>
       </c>
       <c r="S4" t="n">
-        <v>41000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>루멘텀 폭등에 따른 수혜주로 언급되며 20% 이상 상승 기대. 실적 오해도 해소되며 긍정적 전망.</t>
+          <t>하이닉스 물량 완판 및 광주반도체 속도전 돌입. 외국인 및 기타 법인 매수세 유입에 따른 상승 기대감.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['루멘텀', 'RF머트리얼즈', '실적']</t>
+          <t>['반도체', '외국인 매수', '대장주']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>079650</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>서산</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7930</v>
+        <v>37200</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+6.44%</t>
+          <t>'+6.90%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-1.04</v>
+        <v>-0.74</v>
       </c>
       <c r="E5" t="n">
-        <v>134</v>
+        <v>48</v>
       </c>
       <c r="F5" t="n">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="G5" t="n">
-        <v>196</v>
+        <v>120</v>
       </c>
       <c r="H5" t="n">
-        <v>0.42</v>
+        <v>5.8</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>7450</v>
+        <v>34800</v>
       </c>
       <c r="K5" t="n">
-        <v>7470</v>
+        <v>36600</v>
       </c>
       <c r="L5" t="n">
-        <v>9680</v>
+        <v>40200</v>
       </c>
       <c r="M5" t="n">
-        <v>7360</v>
+        <v>36200</v>
       </c>
       <c r="N5" t="n">
-        <v>1.46</v>
+        <v>6.54</v>
       </c>
       <c r="O5" t="n">
-        <v>91734271935</v>
+        <v>92502227625</v>
       </c>
       <c r="P5" t="n">
-        <v>10300</v>
+        <v>126600</v>
       </c>
       <c r="Q5" t="n">
-        <v>952</v>
+        <v>15260</v>
       </c>
       <c r="R5" t="n">
-        <v>506000</v>
+        <v>52000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>41000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>하이닉스 물량 완판 및 광주반도체 관련 언급. 외인 매수세에 대한 긍정적 기대감 존재.</t>
+          <t>루멘텀 급등 및 마벨 테크놀로지 인수설. RF 머트리얼즈 최고 수혜주 언급 및 3분기 실적 개선 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['루멘텀', 'RF그룹주', '실적']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>079650</t>
+          <t>327260</t>
         </is>
       </c>
     </row>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14750</v>
+        <v>14950</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+2.50%</t>
+          <t>'+3.89%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.06</v>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F6" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G6" t="n">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="H6" t="n">
         <v>8.050000000000001</v>
@@ -978,7 +978,7 @@
         <v>8.109999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>43193585785</v>
+        <v>44665908130</v>
       </c>
       <c r="P6" t="n">
         <v>49800</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>미국 의료 AI 섹터 급등 및 템퍼스AI 관련 언급. 공매도 세력에 대한 공격적인 심리 표현.</t>
+          <t>미국 의료 AI 섹터 급등 및 템퍼스 AI 상승. 공매도 세력과의 대립 및 보유 비중 관리 중요성 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['의료AI', '공매도']</t>
+          <t>['의료 AI', '공매도', '숏스퀴즈']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,83 +1023,83 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1500000</v>
+        <v>29100</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.87%</t>
+          <t>'+1.39%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="E7" t="n">
-        <v>800</v>
+        <v>40</v>
       </c>
       <c r="F7" t="n">
-        <v>490</v>
+        <v>27</v>
       </c>
       <c r="G7" t="n">
-        <v>1407</v>
+        <v>58</v>
       </c>
       <c r="H7" t="n">
-        <v>48.66</v>
+        <v>1.77</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1487000</v>
+        <v>28700</v>
       </c>
       <c r="K7" t="n">
-        <v>1511000</v>
+        <v>29150</v>
       </c>
       <c r="L7" t="n">
-        <v>1587000</v>
+        <v>31400</v>
       </c>
       <c r="M7" t="n">
-        <v>1493000</v>
+        <v>28350</v>
       </c>
       <c r="N7" t="n">
-        <v>48.61</v>
+        <v>1.73</v>
       </c>
       <c r="O7" t="n">
-        <v>3316253166000</v>
+        <v>87240012250</v>
       </c>
       <c r="P7" t="n">
-        <v>2987000</v>
+        <v>59600</v>
       </c>
       <c r="Q7" t="n">
-        <v>501000</v>
+        <v>1850</v>
       </c>
       <c r="R7" t="n">
-        <v>281000</v>
+        <v>-42000</v>
       </c>
       <c r="S7" t="n">
-        <v>-134000</v>
+        <v>11000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>주주환원 정책 호조와 실적 개선 기대감으로 인한 긍정적 주가 전망.</t>
+          <t>루멘텀홀딩스 인수 관련 호재 및 기관 매수세 언급. 광통신주 동반 하락으로 인한 관망세.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['SK하이닉스', '주주환원', '실적']</t>
+          <t>['루멘텀', '기관']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,90 +1108,90 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>043260</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28650</v>
+        <v>1496000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-0.17%</t>
+          <t>'+0.61%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>40</v>
+        <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>27</v>
+        <v>487</v>
       </c>
       <c r="G8" t="n">
-        <v>58</v>
+        <v>1156</v>
       </c>
       <c r="H8" t="n">
-        <v>1.77</v>
+        <v>48.66</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>28700</v>
+        <v>1487000</v>
       </c>
       <c r="K8" t="n">
-        <v>29150</v>
+        <v>1511000</v>
       </c>
       <c r="L8" t="n">
-        <v>31400</v>
+        <v>1587000</v>
       </c>
       <c r="M8" t="n">
-        <v>28350</v>
+        <v>1479000</v>
       </c>
       <c r="N8" t="n">
-        <v>1.73</v>
+        <v>48.61</v>
       </c>
       <c r="O8" t="n">
-        <v>84195679575</v>
+        <v>3633575368000</v>
       </c>
       <c r="P8" t="n">
-        <v>59600</v>
+        <v>2987000</v>
       </c>
       <c r="Q8" t="n">
-        <v>1850</v>
+        <v>501000</v>
       </c>
       <c r="R8" t="n">
-        <v>-42000</v>
+        <v>281000</v>
       </c>
       <c r="S8" t="n">
-        <v>11000</v>
+        <v>-134000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>루멘텀홀딩스 인수 관련 호재 및 기관 매수세 언급. 광통신주 동반 하락으로 인한 관망세.</t>
+          <t>타사 대비 상대적 우위 및 시장 내 역할 강조. 포모 유발 및 꾸준한 매수 권유.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['루멘텀', '기관']</t>
+          <t>['상대적 우위', '시장 내 역할', '꾸준한 매수']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,86 +1200,86 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>043260</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>63400</v>
+        <v>14840</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.25%</t>
+          <t>'-0.93%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.54</v>
+        <v>0.46</v>
       </c>
       <c r="E9" t="n">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="F9" t="n">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="G9" t="n">
-        <v>381</v>
+        <v>637</v>
       </c>
       <c r="H9" t="n">
-        <v>41.55</v>
+        <v>3.33</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>64200</v>
+        <v>14980</v>
       </c>
       <c r="K9" t="n">
-        <v>64200</v>
+        <v>15120</v>
       </c>
       <c r="L9" t="n">
-        <v>65500</v>
+        <v>15950</v>
       </c>
       <c r="M9" t="n">
-        <v>62500</v>
+        <v>14600</v>
       </c>
       <c r="N9" t="n">
-        <v>41.01</v>
+        <v>2.87</v>
       </c>
       <c r="O9" t="n">
-        <v>113927230000</v>
+        <v>123842964345</v>
       </c>
       <c r="P9" t="n">
-        <v>67300</v>
+        <v>31500</v>
       </c>
       <c r="Q9" t="n">
-        <v>23150</v>
+        <v>1819</v>
       </c>
       <c r="R9" t="n">
-        <v>271000</v>
+        <v>-213000</v>
       </c>
       <c r="S9" t="n">
-        <v>-21000</v>
+        <v>41000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>수주 공시 및 자사주 매입 소각 예정에 따른 신고가 경신 기대감.</t>
+          <t>메타 관련 뉴스 및 루멘텀 급등에 따른 광통신 섹터 관심 증대. 연말 목표 주가 3만 원 전망.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['삼성E&amp;A', '수주공시', '자사주소각']</t>
+          <t>['광통신', '메타', '실적 전망']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1292,86 +1292,86 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14670</v>
+        <v>62900</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.07%</t>
+          <t>'-2.02%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.46</v>
+        <v>0.54</v>
       </c>
       <c r="E10" t="n">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="F10" t="n">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="G10" t="n">
-        <v>618</v>
+        <v>397</v>
       </c>
       <c r="H10" t="n">
-        <v>3.33</v>
+        <v>41.55</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>14980</v>
+        <v>64200</v>
       </c>
       <c r="K10" t="n">
-        <v>15120</v>
+        <v>64200</v>
       </c>
       <c r="L10" t="n">
-        <v>15950</v>
+        <v>65500</v>
       </c>
       <c r="M10" t="n">
-        <v>14600</v>
+        <v>62500</v>
       </c>
       <c r="N10" t="n">
-        <v>2.87</v>
+        <v>41.01</v>
       </c>
       <c r="O10" t="n">
-        <v>121681239105</v>
+        <v>120525779450</v>
       </c>
       <c r="P10" t="n">
-        <v>31500</v>
+        <v>67300</v>
       </c>
       <c r="Q10" t="n">
-        <v>1819</v>
+        <v>23150</v>
       </c>
       <c r="R10" t="n">
-        <v>-213000</v>
+        <v>271000</v>
       </c>
       <c r="S10" t="n">
-        <v>41000</v>
+        <v>-21000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>메타 관련 뉴스 및 3분기 예상 실적 언급. 루멘텀 인수 관련 호재 및 반도체 공정용 레이저 히터 제어 특허 등록 사실 포함.</t>
+          <t>자사주 매입 및 소각 기대감, 수주 공시 임박 및 신고가 도전 가능성 언급. 반도체 부문 투자 확대 수혜 전망.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['메타', '루멘텀']</t>
+          <t>['자사주 소각', '수주 공시', '신고가 도전']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>520000</v>
+        <v>184000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-2.62%</t>
+          <t>'-3.21%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.08</v>
+        <v>0.1</v>
       </c>
       <c r="E11" t="n">
-        <v>228</v>
+        <v>103</v>
       </c>
       <c r="F11" t="n">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="G11" t="n">
-        <v>989</v>
+        <v>259</v>
       </c>
       <c r="H11" t="n">
-        <v>24.78</v>
+        <v>75</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>534000</v>
+        <v>190100</v>
       </c>
       <c r="K11" t="n">
-        <v>546000</v>
+        <v>189400</v>
       </c>
       <c r="L11" t="n">
-        <v>563000</v>
+        <v>197000</v>
       </c>
       <c r="M11" t="n">
-        <v>516000</v>
+        <v>181200</v>
       </c>
       <c r="N11" t="n">
-        <v>24.86</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>332653431000</v>
+        <v>910780750200</v>
       </c>
       <c r="P11" t="n">
-        <v>723000</v>
+        <v>243500</v>
       </c>
       <c r="Q11" t="n">
-        <v>259000</v>
+        <v>71000</v>
       </c>
       <c r="R11" t="n">
-        <v>6000</v>
+        <v>-484000</v>
       </c>
       <c r="S11" t="n">
-        <v>5000</v>
+        <v>-1000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>26년 3분기 연결 영업이익 컨센서스 상회 및 호실적 발표. ESS, 전고체 관련주 동반 상승. 긍정적 전망.</t>
+          <t>오너 리스크 및 주주환원 불확실성에 대한 불만. 우선주 매입 및 소각 관련 불명확한 입장.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['영업이익', '컨센서스', 'ESS']</t>
+          <t>['오너 리스크', '주주환원', '우선주']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>184200</v>
+        <v>516000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.10%</t>
+          <t>'-3.37%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.1</v>
+        <v>-0.08</v>
       </c>
       <c r="E12" t="n">
-        <v>85</v>
+        <v>240</v>
       </c>
       <c r="F12" t="n">
-        <v>62</v>
+        <v>126</v>
       </c>
       <c r="G12" t="n">
-        <v>214</v>
+        <v>1051</v>
       </c>
       <c r="H12" t="n">
-        <v>75</v>
+        <v>24.78</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>190100</v>
+        <v>534000</v>
       </c>
       <c r="K12" t="n">
-        <v>189400</v>
+        <v>546000</v>
       </c>
       <c r="L12" t="n">
-        <v>197000</v>
+        <v>563000</v>
       </c>
       <c r="M12" t="n">
-        <v>182100</v>
+        <v>512000</v>
       </c>
       <c r="N12" t="n">
-        <v>74.90000000000001</v>
+        <v>24.86</v>
       </c>
       <c r="O12" t="n">
-        <v>854155574150</v>
+        <v>347038614500</v>
       </c>
       <c r="P12" t="n">
-        <v>243500</v>
+        <v>723000</v>
       </c>
       <c r="Q12" t="n">
-        <v>71000</v>
+        <v>259000</v>
       </c>
       <c r="R12" t="n">
-        <v>-484000</v>
+        <v>6000</v>
       </c>
       <c r="S12" t="n">
-        <v>-1000</v>
+        <v>5000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>주주환원 불확실성과 오너 리스크에 대한 우려.</t>
+          <t>26년 3분기 컨센서스 상회하는 영업이익 달성. ESS, 전고체 관련주 상승 및 고점 재돌파 기대.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.15</v>
+        <v>0.6</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['우선주', '주주환원', '이재용']</t>
+          <t>['실적', '영업이익', '컨퍼런스콜']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>006400</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>15950</v>
+        <v>8850</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.39%</t>
+          <t>'-3.59%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.04</v>
+        <v>-0.37</v>
       </c>
       <c r="E13" t="n">
-        <v>97</v>
+        <v>53</v>
       </c>
       <c r="F13" t="n">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="G13" t="n">
-        <v>239</v>
+        <v>139</v>
       </c>
       <c r="H13" t="n">
-        <v>28.07</v>
+        <v>0.37</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>16510</v>
+        <v>9180</v>
       </c>
       <c r="K13" t="n">
-        <v>16380</v>
+        <v>9200</v>
       </c>
       <c r="L13" t="n">
-        <v>16440</v>
+        <v>10900</v>
       </c>
       <c r="M13" t="n">
-        <v>15770</v>
+        <v>8730</v>
       </c>
       <c r="N13" t="n">
-        <v>28.03</v>
+        <v>0.74</v>
       </c>
       <c r="O13" t="n">
-        <v>27470174790</v>
+        <v>28616942705</v>
       </c>
       <c r="P13" t="n">
-        <v>35350</v>
+        <v>19380</v>
       </c>
       <c r="Q13" t="n">
-        <v>15770</v>
+        <v>3200</v>
       </c>
       <c r="R13" t="n">
-        <v>-348000</v>
+        <v>-32000</v>
       </c>
       <c r="S13" t="n">
-        <v>-70000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>실적 부진과 향후 전망에 대한 부정적인 평가.</t>
+          <t>주가 조작 및 경영진에 대한 강한 불신 표출. 주가 하락 및 거래량 부진에 대한 불만.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['삼성중공업', '실적', '조선주']</t>
+          <t>['주가 조작', '경영진 불신', '거래량 부진']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>25750</v>
+        <v>25700</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.56%</t>
+          <t>'-3.75%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1688,7 +1688,7 @@
         <v>37</v>
       </c>
       <c r="G14" t="n">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="H14" t="n">
         <v>12.23</v>
@@ -1714,7 +1714,7 @@
         <v>12.3</v>
       </c>
       <c r="O14" t="n">
-        <v>23787009900</v>
+        <v>25649260600</v>
       </c>
       <c r="P14" t="n">
         <v>59300</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>실적 발표를 앞두고 불확실성이 존재하며, 시장 상황 및 실적 결과에 따른 주가 변동 가능성.</t>
+          <t>실적 발표 예정 및 태양광 섹터 하락세 영향. 실적에 따른 매수 타이밍 고려 및 변동성 예상.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['한화솔루션', '실적발표', '태양광']</t>
+          <t>['실적 발표', '태양광 섹터', '매수 타이밍']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1759,31 +1759,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8820</v>
+        <v>15880</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.92%</t>
+          <t>'-3.82%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.37</v>
+        <v>0.04</v>
       </c>
       <c r="E15" t="n">
-        <v>49</v>
+        <v>102</v>
       </c>
       <c r="F15" t="n">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="G15" t="n">
-        <v>123</v>
+        <v>244</v>
       </c>
       <c r="H15" t="n">
-        <v>0.37</v>
+        <v>28.07</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>9180</v>
+        <v>16510</v>
       </c>
       <c r="K15" t="n">
-        <v>9200</v>
+        <v>16380</v>
       </c>
       <c r="L15" t="n">
-        <v>10900</v>
+        <v>16440</v>
       </c>
       <c r="M15" t="n">
-        <v>8730</v>
+        <v>15770</v>
       </c>
       <c r="N15" t="n">
-        <v>0.74</v>
+        <v>28.03</v>
       </c>
       <c r="O15" t="n">
-        <v>28274519195</v>
+        <v>29408814930</v>
       </c>
       <c r="P15" t="n">
-        <v>19380</v>
+        <v>35350</v>
       </c>
       <c r="Q15" t="n">
-        <v>3200</v>
+        <v>15770</v>
       </c>
       <c r="R15" t="n">
-        <v>-32000</v>
+        <v>-348000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-70000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>주가 조작 및 투명성 부족에 대한 강한 불만. 외인 매도세 확인.</t>
+          <t>주가 하락세 및 실적 발표에 대한 우려. 중국과의 경쟁 열위 및 주가조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['주가조작', '외인매도', '투명성']</t>
+          <t>['주가 하락', '실적 발표', '중국 경쟁']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,77 +1844,77 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>230750</v>
+        <v>3990</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.65%</t>
+          <t>'-4.89%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.04</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>800</v>
+        <v>79</v>
       </c>
       <c r="F16" t="n">
-        <v>617</v>
+        <v>60</v>
       </c>
       <c r="G16" t="n">
-        <v>2312</v>
+        <v>202</v>
       </c>
       <c r="H16" t="n">
-        <v>46.19</v>
+        <v>2.2</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>242000</v>
+        <v>4195</v>
       </c>
       <c r="K16" t="n">
-        <v>241000</v>
+        <v>4280</v>
       </c>
       <c r="L16" t="n">
-        <v>249000</v>
+        <v>4480</v>
       </c>
       <c r="M16" t="n">
-        <v>229000</v>
+        <v>3915</v>
       </c>
       <c r="N16" t="n">
-        <v>46.15</v>
+        <v>1.2</v>
       </c>
       <c r="O16" t="n">
-        <v>2967778712000</v>
+        <v>150472084194</v>
       </c>
       <c r="P16" t="n">
-        <v>374500</v>
+        <v>8100</v>
       </c>
       <c r="Q16" t="n">
-        <v>94500</v>
+        <v>592</v>
       </c>
       <c r="R16" t="n">
-        <v>166000</v>
+        <v>-347000</v>
       </c>
       <c r="S16" t="n">
-        <v>-505000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>낮은 주주환원 정책에 대한 비판과 실적 대비 부진한 주가 흐름.</t>
+          <t>루멘텀 5G 상용화망 성공 뉴스에 따른 급등락 반복. 단기 차익 매물 출회 및 개인 투자자 대응 전략 논쟁.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,11 +1923,11 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['주주환원', '영업이익', '삼성전자']</t>
+          <t>['5G 상용화', '광통신', '단타']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,90 +1936,90 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3960</v>
+        <v>229500</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-5.60%</t>
+          <t>'-5.17%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0.04</v>
       </c>
       <c r="E17" t="n">
-        <v>74</v>
+        <v>800</v>
       </c>
       <c r="F17" t="n">
-        <v>56</v>
+        <v>618</v>
       </c>
       <c r="G17" t="n">
-        <v>199</v>
+        <v>2458</v>
       </c>
       <c r="H17" t="n">
-        <v>2.2</v>
+        <v>46.19</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>4195</v>
+        <v>242000</v>
       </c>
       <c r="K17" t="n">
-        <v>4280</v>
+        <v>241000</v>
       </c>
       <c r="L17" t="n">
-        <v>4480</v>
+        <v>249000</v>
       </c>
       <c r="M17" t="n">
-        <v>3915</v>
+        <v>227000</v>
       </c>
       <c r="N17" t="n">
-        <v>1.2</v>
+        <v>46.15</v>
       </c>
       <c r="O17" t="n">
-        <v>149207535270</v>
+        <v>3222406275000</v>
       </c>
       <c r="P17" t="n">
-        <v>8100</v>
+        <v>374500</v>
       </c>
       <c r="Q17" t="n">
-        <v>592</v>
+        <v>94500</v>
       </c>
       <c r="R17" t="n">
-        <v>-347000</v>
+        <v>166000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-505000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>광통신 관련 긍정적 뉴스에 따른 기대감과 함께 변동성이 큰 종목.</t>
+          <t>경영진 및 주주환원 정책에 대한 강한 불만 표출. 이재용 구속 및 경영진 교체 요구.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.35</v>
+        <v>0.05</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['광통신', '루멘텀', '빛과전자']</t>
+          <t>['주주환원', '경영진 교체', '이재용']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17350</v>
+        <v>17200</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-9.68%</t>
+          <t>'-10.46%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.46</v>
       </c>
       <c r="E18" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F18" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G18" t="n">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="H18" t="n">
         <v>0.65</v>
@@ -2076,13 +2076,13 @@
         <v>19840</v>
       </c>
       <c r="M18" t="n">
-        <v>17090</v>
+        <v>17060</v>
       </c>
       <c r="N18" t="n">
         <v>1.11</v>
       </c>
       <c r="O18" t="n">
-        <v>77320221280</v>
+        <v>78735405725</v>
       </c>
       <c r="P18" t="n">
         <v>28800</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>보호예수 물량 및 대규모 매도 가능성 언급. 반도체 섹터 전반의 하락세 및 주가 폭락 우려.</t>
+          <t>보호예수 물량 및 주포의 매도 가능성 언급. 반도체 대폭락 및 하락 VI 발동 우려.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['보호예수', '반도체']</t>
+          <t>['보호예수', '하락 vi', '반도체']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1878</v>
+        <v>1859</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-10.57%</t>
+          <t>'-11.48%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.28</v>
       </c>
       <c r="E19" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F19" t="n">
         <v>34</v>
       </c>
       <c r="G19" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H19" t="n">
         <v>5.35</v>
@@ -2174,7 +2174,7 @@
         <v>5.07</v>
       </c>
       <c r="O19" t="n">
-        <v>10723121306</v>
+        <v>11032611792</v>
       </c>
       <c r="P19" t="n">
         <v>4980</v>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>54900</v>
+        <v>54200</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-10.59%</t>
+          <t>'-11.73%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0.02</v>
       </c>
       <c r="E20" t="n">
-        <v>598</v>
+        <v>639</v>
       </c>
       <c r="F20" t="n">
-        <v>423</v>
+        <v>443</v>
       </c>
       <c r="G20" t="n">
-        <v>1697</v>
+        <v>1868</v>
       </c>
       <c r="H20" t="n">
         <v>22.34</v>
@@ -2266,7 +2266,7 @@
         <v>22.32</v>
       </c>
       <c r="O20" t="n">
-        <v>207427682700</v>
+        <v>219736253050</v>
       </c>
       <c r="P20" t="n">
         <v>139200</v>
@@ -2282,16 +2282,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>체코 원전 사업 관련, 시공사 변경에도 불구하고 두산에너빌리티의 영향은 제한적이라는 분석.</t>
+          <t>체코 원전 사업 시공사 변경 관련 논란. 두산에너빌리티는 기자재 공급으로 영향 제한적이라는 분석.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['체코 원전', '두산에너빌리티', '시공사']</t>
+          <t>['체코 원전', '시공사 변경', '기자재 공급']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2220</v>
+        <v>2190</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-13.62%</t>
+          <t>'-14.79%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>-0.47</v>
       </c>
       <c r="E21" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F21" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G21" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H21" t="n">
         <v>1.22</v>
@@ -2352,13 +2352,13 @@
         <v>2575</v>
       </c>
       <c r="M21" t="n">
-        <v>2205</v>
+        <v>2187</v>
       </c>
       <c r="N21" t="n">
         <v>1.69</v>
       </c>
       <c r="O21" t="n">
-        <v>12026993982</v>
+        <v>12553522936</v>
       </c>
       <c r="P21" t="n">
         <v>2965</v>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>전환사채 발행 및 대규모 매물 출회 관련 언급. 주가 하락에 대한 답답함 토로.</t>
+          <t>전환사채 발행 및 매물 출회 가능성 제기. 주가 급락 및 투자자 답답함 호소.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['전환사채', '매물폭탄']</t>
+          <t>['전환사채', '매물폭탄', '실적']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>11370</v>
+        <v>11150</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-20.32%</t>
+          <t>'-21.86%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-0.23</v>
       </c>
       <c r="E22" t="n">
-        <v>493</v>
+        <v>535</v>
       </c>
       <c r="F22" t="n">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="G22" t="n">
-        <v>1077</v>
+        <v>1233</v>
       </c>
       <c r="H22" t="n">
         <v>9.6</v>
@@ -2450,7 +2450,7 @@
         <v>9.83</v>
       </c>
       <c r="O22" t="n">
-        <v>216673479785</v>
+        <v>226299345300</v>
       </c>
       <c r="P22" t="n">
         <v>40350</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>체코 원전 사업 관련 불확실성으로 인한 주가 하락 및 향후 전망 불투명.</t>
+          <t>체코 원전 사업 관련 부정적 뉴스 및 증권사 목표가 하향에 따른 주가 하락 우려. 과매도 구간 진입 가능성 제시.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['체코 원전', '대우건설', '사업 파기']</t>
+          <t>['체코 원전', '목표가 하향', '과매도']</t>
         </is>
       </c>
       <c r="X22" t="n">
